--- a/docs/src/business/caddie-assignment-simulation.xlsx
+++ b/docs/src/business/caddie-assignment-simulation.xlsx
@@ -2,14 +2,45 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定・説明" sheetId="1" r:id="Raaca6b53ca404d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キャディ条件" sheetId="2" r:id="Rd95ca6533d8f48fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラウンド入力" sheetId="3" r:id="R66478396331341de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="割当シミュレーション" sheetId="4" r:id="R4702561adc474032"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人集計" sheetId="5" r:id="R1118fa4704394c2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シチュエーション例" sheetId="6" r:id="R5925901859e741ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定・説明" sheetId="1" r:id="Rcf11fd7e8b0b47b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キャディ条件" sheetId="2" r:id="Re52a65fec4914587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラウンド入力" sheetId="3" r:id="R89f6e98413214c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="割当シミュレーション" sheetId="4" r:id="R0b0e36ea280740a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人集計" sheetId="5" r:id="R1f8721b9b67849c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シチュエーション例" sheetId="6" r:id="Rd66f3fcf7f67403b"/>
   </x:sheets>
 </x:workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:authors>
+    <x:author>tc={CB6272FC-33C8-4F64-9B09-F10D105AD59B}</x:author>
+    <x:author>tc={EBEBC430-A8BF-4E0C-9FAC-6CDB406E34BB}</x:author>
+  </x:authors>
+  <x:commentList>
+    <x:comment ref="F4" authorId="0">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    有効スコアは負数でも割当可能です。-9999だけをHard不適合の番兵値として扱います。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+    <x:comment ref="L4" authorId="1">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    公平性は既存実績に先行行の今回割当を加えて再計算します。2R希望ボーナスは成立可能なペアにだけ適用します。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
+  </x:commentList>
+</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -44,7 +75,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -81,8 +112,18 @@
         <x:fgColor rgb="FFFFF4D6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3E7858"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="16">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -222,11 +263,25 @@
         <x:color rgb="FFCAD5CE"/>
       </x:left>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC8D7CE"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC8D7CE"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC8D7CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC8D7CE"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="112">
+  <x:cellXfs count="118">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -443,18 +498,26 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="9">
+  <x:dxfs count="10">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FFA61B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -465,7 +528,7 @@
         <x:color rgb="FFA61B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -476,7 +539,7 @@
         <x:color rgb="FFA61B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -486,7 +549,7 @@
         <x:color rgb="FFA61B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -497,7 +560,7 @@
         <x:color rgb="FFA61B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -507,7 +570,7 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F2FA"/>
         </x:patternFill>
       </x:fill>
@@ -517,7 +580,7 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE8F1EA"/>
         </x:patternFill>
       </x:fill>
@@ -527,7 +590,7 @@
         <x:b/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -538,13 +601,30 @@
         <x:color rgb="FF5B347D"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFEEE7F7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB42318"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFEEE7F7"/>
+          <x:bgColor rgb="FFFDE2E1"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="takanorifukuyama" id="{5643E6F5-16A3-4CB8-B8BE-2EE965868968}"/>
+</xltc:personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -738,6 +818,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="F4" dT="2026-09-01T08:01:09.932" personId="{5643E6F5-16A3-4CB8-B8BE-2EE965868968}" id="{CB6272FC-33C8-4F64-9B09-F10D105AD59B}">
+    <xltc:text>有効スコアは負数でも割当可能です。-9999だけをHard不適合の番兵値として扱います。</xltc:text>
+  </xltc:threadedComment>
+  <xltc:threadedComment ref="L4" dT="2026-09-01T08:01:09.938" personId="{5643E6F5-16A3-4CB8-B8BE-2EE965868968}" id="{EBEBC430-A8BF-4E0C-9FAC-6CDB406E34BB}">
+    <xltc:text>公平性は既存実績に先行行の今回割当を加えて再計算します。2R希望ボーナスは成立可能なペアにだけ適用します。</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -872,6 +963,13 @@
       <x:c r="B10" s="18" t="n">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="D10" t="str">
+        <x:v>入力エラー</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
+        <x:f>COUNTIF('キャディ条件'!$O$5:$O$14,"重複ID*")</x:f>
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -917,7 +1015,7 @@
         <x:v>Hard条件</x:v>
       </x:c>
       <x:c r="C16" s="31" t="str">
-        <x:v>勤務区分（土日・平日）、最大組人数、担当可能コース、最大ラウンド数、時間重複を満たさない候補は -9999 点。</x:v>
+        <x:v>勤務区分、ID一意性、2R可、最大組人数、担当可能コース、最大ラウンド数、時間重複を満たさない候補は -9999 点。</x:v>
       </x:c>
       <x:c r="D16" s="31"/>
       <x:c r="E16" s="31"/>
@@ -949,7 +1047,7 @@
         <x:v>希望</x:v>
       </x:c>
       <x:c r="C18" s="34" t="str">
-        <x:v>希望組人数、当日2ラウンド希望、4人組のベテラン適性を加点する。</x:v>
+        <x:v>希望組人数、成立可能な当日2ラウンド希望、4人組のベテラン適性を加点する。</x:v>
       </x:c>
       <x:c r="D18" s="34"/>
       <x:c r="E18" s="34"/>
@@ -965,7 +1063,7 @@
         <x:v>公平性</x:v>
       </x:c>
       <x:c r="C19" s="34" t="str">
-        <x:v>既存の月間担当数・4人組数が多いほど減点する。重みは上の設定で変更可能。</x:v>
+        <x:v>既存実績に加え、先行行で確定した今回割当も累積して公平性を再計算する。重みは上の設定で変更可能。</x:v>
       </x:c>
       <x:c r="D19" s="34"/>
       <x:c r="E19" s="34"/>
@@ -1087,6 +1185,7 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -1109,7 +1208,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>青いセルを編集してください。Hard条件と希望を分けて入力します。空き行にはキャディを追加できます。</x:v>
+        <x:v>青いセルを編集してください。Hard条件と希望を分けて入力します。ID重複は割当を停止します。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -1168,6 +1267,9 @@
       <x:c r="N4" s="60" t="str">
         <x:v>制限の表示文</x:v>
       </x:c>
+      <x:c r="O4" s="115" t="str">
+        <x:v>ID検証</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="61" t="str">
@@ -1212,6 +1314,10 @@
       <x:c r="N5" s="69" t="str">
         <x:v>4人不可・2人組希望</x:v>
       </x:c>
+      <x:c r="O5" s="117" t="str">
+        <x:f>IF(A5="","",IF(COUNTIF($A$5:$A$14,A5)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="61" t="str">
@@ -1256,6 +1362,10 @@
       <x:c r="N6" s="69" t="str">
         <x:v>4人組希望</x:v>
       </x:c>
+      <x:c r="O6" s="117" t="str">
+        <x:f>IF(A6="","",IF(COUNTIF($A$5:$A$14,A6)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="61" t="str">
@@ -1298,6 +1408,10 @@
       <x:c r="N7" s="69" t="str">
         <x:v>当日2ラウンド希望</x:v>
       </x:c>
+      <x:c r="O7" s="117" t="str">
+        <x:f>IF(A7="","",IF(COUNTIF($A$5:$A$14,A7)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="61" t="str">
@@ -1340,6 +1454,10 @@
       <x:c r="N8" s="69" t="str">
         <x:v>平日のみ</x:v>
       </x:c>
+      <x:c r="O8" s="117" t="str">
+        <x:f>IF(A8="","",IF(COUNTIF($A$5:$A$14,A8)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+        <x:v>OK</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="61" t="str">
@@ -1381,6 +1499,10 @@
       </x:c>
       <x:c r="N9" s="69" t="str">
         <x:v>制約なし</x:v>
+      </x:c>
+      <x:c r="O9" s="117" t="str">
+        <x:f>IF(A9="","",IF(COUNTIF($A$5:$A$14,A9)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+        <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1418,6 +1540,9 @@
         <x:v>11000</x:v>
       </x:c>
       <x:c r="N10" s="69"/>
+      <x:c r="O10" s="117" t="str">
+        <x:f>IF(A10="","",IF(COUNTIF($A$5:$A$14,A10)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="61"/>
@@ -1454,6 +1579,9 @@
         <x:v>11000</x:v>
       </x:c>
       <x:c r="N11" s="69"/>
+      <x:c r="O11" s="117" t="str">
+        <x:f>IF(A11="","",IF(COUNTIF($A$5:$A$14,A11)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="61"/>
@@ -1490,6 +1618,9 @@
         <x:v>11000</x:v>
       </x:c>
       <x:c r="N12" s="69"/>
+      <x:c r="O12" s="117" t="str">
+        <x:f>IF(A12="","",IF(COUNTIF($A$5:$A$14,A12)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="61"/>
@@ -1526,6 +1657,9 @@
         <x:v>11000</x:v>
       </x:c>
       <x:c r="N13" s="69"/>
+      <x:c r="O13" s="117" t="str">
+        <x:f>IF(A13="","",IF(COUNTIF($A$5:$A$14,A13)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="63"/>
@@ -1562,12 +1696,18 @@
         <x:v>11000</x:v>
       </x:c>
       <x:c r="N14" s="70"/>
+      <x:c r="O14" s="117" t="str">
+        <x:f>IF(A14="","",IF(COUNTIF($A$5:$A$14,A14)&gt;1,"重複ID（割当停止）","OK"))</x:f>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:N1"/>
-    <x:mergeCell ref="A2:N2"/>
+    <x:mergeCell ref="A1:O1"/>
+    <x:mergeCell ref="A2:O2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="O5:O14">
+    <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="重複ID"/>
+  </x:conditionalFormatting>
   <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="C5:C14">
       <x:formula1>"全日,土日,平日"</x:formula1>
@@ -1607,7 +1747,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>ラウンド入力（架空の土曜日）</x:v>
+        <x:v>ラウンド入力（対象日連動）</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1616,7 +1756,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>開始時刻の昇順で入力してください。所要時間が空欄なら設定シートの既定値を使います。</x:v>
+        <x:v>開始時刻の順で入力してください。日付は設定シートの対象日に連動し、所要時間が空欄なら既定値を使います。</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -1645,6 +1785,7 @@
         <x:v>R1</x:v>
       </x:c>
       <x:c r="B5" s="71" t="n">
+        <x:f>IF(A5="","",'設定・説明'!$B$5+TIME(7,0,0))</x:f>
         <x:v>46270.291666666664</x:v>
       </x:c>
       <x:c r="C5" s="62" t="n">
@@ -1662,6 +1803,7 @@
         <x:v>R2</x:v>
       </x:c>
       <x:c r="B6" s="71" t="n">
+        <x:f>IF(A6="","",'設定・説明'!$B$5+TIME(7,20,0))</x:f>
         <x:v>46270.305555555555</x:v>
       </x:c>
       <x:c r="C6" s="62" t="n">
@@ -1679,6 +1821,7 @@
         <x:v>R3</x:v>
       </x:c>
       <x:c r="B7" s="71" t="n">
+        <x:f>IF(A7="","",'設定・説明'!$B$5+TIME(8,0,0))</x:f>
         <x:v>46270.333333333336</x:v>
       </x:c>
       <x:c r="C7" s="62" t="n">
@@ -1696,6 +1839,7 @@
         <x:v>R4</x:v>
       </x:c>
       <x:c r="B8" s="71" t="n">
+        <x:f>IF(A8="","",'設定・説明'!$B$5+TIME(13,30,0))</x:f>
         <x:v>46270.5625</x:v>
       </x:c>
       <x:c r="C8" s="62" t="n">
@@ -1713,6 +1857,7 @@
         <x:v>R5</x:v>
       </x:c>
       <x:c r="B9" s="71" t="n">
+        <x:f>IF(A9="","",'設定・説明'!$B$5+TIME(14,0,0))</x:f>
         <x:v>46270.583333333336</x:v>
       </x:c>
       <x:c r="C9" s="62" t="n">
@@ -2043,7 +2188,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F5" s="74" t="str">
-        <x:f>IF($A5="","",IF(MAX(L5:U5)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L5:U5),L5:U5,0))))</x:f>
+        <x:f>IF($A5="","",IF(COUNTIF(L5:U5,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L5:U5),L5:U5,0))))</x:f>
         <x:v>cad_tanaka</x:v>
       </x:c>
       <x:c r="G5" s="74" t="str">
@@ -2059,46 +2204,46 @@
         <x:v>46270.52083333333</x:v>
       </x:c>
       <x:c r="J5" s="85" t="str">
-        <x:f>IF($A5="","",IF($F5="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F5,'キャディ条件'!$A$5:$A$14,0))=$C5,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F5,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A5="","",IF($F5="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F5,'キャディ条件'!$A$5:$A$14,0))=$C5,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F5,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F5)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
         <x:v>2ラウンド希望を考慮</x:v>
       </x:c>
       <x:c r="K5" s="85" t="str">
         <x:f>IF($A5="","",IF($F5="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L5" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D5),COUNTIF($F$4:F4,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F4,L$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$5=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D5),COUNTIF($F$4:F4,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F4,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F4,L$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$5=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F4,L$3)=1,AND(COUNTIF($F$4:F4,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F4,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F4,L$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="M5" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D5),COUNTIF($F$4:F4,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F4,M$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$6=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D5),COUNTIF($F$4:F4,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F4,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F4,M$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$6=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F4,M$3)=1,AND(COUNTIF($F$4:F4,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F4,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F4,M$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>115</x:v>
       </x:c>
       <x:c r="N5" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D5),COUNTIF($F$4:F4,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F4,N$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$7=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D5),COUNTIF($F$4:F4,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F4,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F4,N$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$7=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F4,N$3)=1,AND(COUNTIF($F$4:F4,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F4,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F4,N$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>127</x:v>
       </x:c>
       <x:c r="O5" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D5),COUNTIF($F$4:F4,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F4,O$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$8=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D5),COUNTIF($F$4:F4,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F4,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F4,O$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$8=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F4,O$3)=1,AND(COUNTIF($F$4:F4,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F4,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F4,O$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="P5" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D5),COUNTIF($F$4:F4,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F4,P$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$9=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D5),COUNTIF($F$4:F4,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F4,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F4,P$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$9=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F4,P$3)=1,AND(COUNTIF($F$4:F4,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F4,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F4,P$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q5" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D5),COUNTIF($F$4:F4,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F4,Q$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$10=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D5),COUNTIF($F$4:F4,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F4,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F4,Q$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$10=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F4,Q$3)=1,AND(COUNTIF($F$4:F4,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F4,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F4,Q$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R5" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D5),COUNTIF($F$4:F4,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F4,R$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$11=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D5),COUNTIF($F$4:F4,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F4,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F4,R$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$11=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F4,R$3)=1,AND(COUNTIF($F$4:F4,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F4,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F4,R$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S5" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D5),COUNTIF($F$4:F4,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F4,S$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$12=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D5),COUNTIF($F$4:F4,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F4,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F4,S$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$12=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F4,S$3)=1,AND(COUNTIF($F$4:F4,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F4,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F4,S$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T5" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D5),COUNTIF($F$4:F4,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F4,T$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$13=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D5),COUNTIF($F$4:F4,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F4,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F4,T$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$13=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F4,T$3)=1,AND(COUNTIF($F$4:F4,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F4,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F4,T$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U5" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A5=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D5),COUNTIF($F$4:F4,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F4,U$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$14=$C5,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C5=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D5),COUNTIF($F$4:F4,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F4,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F4,U$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$14=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F4,U$3)=1,AND(COUNTIF($F$4:F4,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F4,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F4,U$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V5" s="74" t="n">
         <x:f>IF($A5="","",IF($J5="人数希望一致",1,0))</x:f>
@@ -2127,7 +2272,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F6" s="74" t="str">
-        <x:f>IF($A6="","",IF(MAX(L6:U6)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L6:U6),L6:U6,0))))</x:f>
+        <x:f>IF($A6="","",IF(COUNTIF(L6:U6,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L6:U6),L6:U6,0))))</x:f>
         <x:v>cad_sato</x:v>
       </x:c>
       <x:c r="G6" s="74" t="str">
@@ -2143,46 +2288,46 @@
         <x:v>46270.53472222222</x:v>
       </x:c>
       <x:c r="J6" s="85" t="str">
-        <x:f>IF($A6="","",IF($F6="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F6,'キャディ条件'!$A$5:$A$14,0))=$C6,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F6,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A6="","",IF($F6="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F6,'キャディ条件'!$A$5:$A$14,0))=$C6,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F6,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F6)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
         <x:v>人数希望一致</x:v>
       </x:c>
       <x:c r="K6" s="85" t="str">
         <x:f>IF($A6="","",IF($F6="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L6" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D6),COUNTIF($F$4:F5,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F5,L$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$5=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D6),COUNTIF($F$4:F5,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F5,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F5,L$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$5=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F5,L$3)=1,AND(COUNTIF($F$4:F5,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F5,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F5,L$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>122</x:v>
       </x:c>
       <x:c r="M6" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D6),COUNTIF($F$4:F5,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F5,M$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$6=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D6),COUNTIF($F$4:F5,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F5,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F5,M$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$6=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F5,M$3)=1,AND(COUNTIF($F$4:F5,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F5,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F5,M$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>75</x:v>
       </x:c>
       <x:c r="N6" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D6),COUNTIF($F$4:F5,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F5,N$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$7=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D6),COUNTIF($F$4:F5,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F5,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F5,N$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$7=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F5,N$3)=1,AND(COUNTIF($F$4:F5,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F5,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F5,N$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="O6" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D6),COUNTIF($F$4:F5,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F5,O$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$8=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D6),COUNTIF($F$4:F5,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F5,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F5,O$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$8=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F5,O$3)=1,AND(COUNTIF($F$4:F5,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F5,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F5,O$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="P6" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D6),COUNTIF($F$4:F5,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F5,P$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$9=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D6),COUNTIF($F$4:F5,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F5,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F5,P$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$9=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F5,P$3)=1,AND(COUNTIF($F$4:F5,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F5,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F5,P$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q6" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D6),COUNTIF($F$4:F5,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F5,Q$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$10=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D6),COUNTIF($F$4:F5,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F5,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F5,Q$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$10=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F5,Q$3)=1,AND(COUNTIF($F$4:F5,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F5,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F5,Q$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R6" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D6),COUNTIF($F$4:F5,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F5,R$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$11=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D6),COUNTIF($F$4:F5,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F5,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F5,R$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$11=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F5,R$3)=1,AND(COUNTIF($F$4:F5,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F5,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F5,R$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S6" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D6),COUNTIF($F$4:F5,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F5,S$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$12=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D6),COUNTIF($F$4:F5,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F5,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F5,S$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$12=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F5,S$3)=1,AND(COUNTIF($F$4:F5,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F5,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F5,S$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T6" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D6),COUNTIF($F$4:F5,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F5,T$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$13=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D6),COUNTIF($F$4:F5,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F5,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F5,T$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$13=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F5,T$3)=1,AND(COUNTIF($F$4:F5,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F5,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F5,T$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U6" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A6=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D6),COUNTIF($F$4:F5,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F5,U$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$14=$C6,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C6=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D6),COUNTIF($F$4:F5,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F5,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F5,U$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$14=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F5,U$3)=1,AND(COUNTIF($F$4:F5,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F5,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F5,U$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V6" s="74" t="n">
         <x:f>IF($A6="","",IF($J6="人数希望一致",1,0))</x:f>
@@ -2211,7 +2356,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F7" s="74" t="str">
-        <x:f>IF($A7="","",IF(MAX(L7:U7)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L7:U7),L7:U7,0))))</x:f>
+        <x:f>IF($A7="","",IF(COUNTIF(L7:U7,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L7:U7),L7:U7,0))))</x:f>
         <x:v>cad_suzuki</x:v>
       </x:c>
       <x:c r="G7" s="74" t="str">
@@ -2227,46 +2372,46 @@
         <x:v>46270.5625</x:v>
       </x:c>
       <x:c r="J7" s="85" t="str">
-        <x:f>IF($A7="","",IF($F7="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F7,'キャディ条件'!$A$5:$A$14,0))=$C7,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F7,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A7="","",IF($F7="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F7,'キャディ条件'!$A$5:$A$14,0))=$C7,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F7,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F7)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
         <x:v>人数希望一致</x:v>
       </x:c>
       <x:c r="K7" s="85" t="str">
         <x:f>IF($A7="","",IF($F7="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L7" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D7),COUNTIF($F$4:F6,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F6,L$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$5=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D7),COUNTIF($F$4:F6,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F6,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F6,L$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$5=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F6,L$3)=1,AND(COUNTIF($F$4:F6,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F6,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F6,L$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="M7" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D7),COUNTIF($F$4:F6,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F6,M$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$6=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D7),COUNTIF($F$4:F6,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F6,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F6,M$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$6=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F6,M$3)=1,AND(COUNTIF($F$4:F6,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F6,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F6,M$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>115</x:v>
       </x:c>
       <x:c r="N7" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D7),COUNTIF($F$4:F6,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F6,N$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$7=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D7),COUNTIF($F$4:F6,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F6,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F6,N$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$7=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F6,N$3)=1,AND(COUNTIF($F$4:F6,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F6,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F6,N$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="O7" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D7),COUNTIF($F$4:F6,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F6,O$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$8=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D7),COUNTIF($F$4:F6,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F6,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F6,O$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$8=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F6,O$3)=1,AND(COUNTIF($F$4:F6,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F6,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F6,O$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="P7" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D7),COUNTIF($F$4:F6,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F6,P$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$9=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D7),COUNTIF($F$4:F6,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F6,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F6,P$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$9=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F6,P$3)=1,AND(COUNTIF($F$4:F6,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F6,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F6,P$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q7" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D7),COUNTIF($F$4:F6,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F6,Q$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$10=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D7),COUNTIF($F$4:F6,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F6,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F6,Q$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$10=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F6,Q$3)=1,AND(COUNTIF($F$4:F6,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F6,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F6,Q$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R7" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D7),COUNTIF($F$4:F6,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F6,R$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$11=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D7),COUNTIF($F$4:F6,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F6,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F6,R$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$11=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F6,R$3)=1,AND(COUNTIF($F$4:F6,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F6,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F6,R$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S7" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D7),COUNTIF($F$4:F6,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F6,S$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$12=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D7),COUNTIF($F$4:F6,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F6,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F6,S$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$12=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F6,S$3)=1,AND(COUNTIF($F$4:F6,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F6,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F6,S$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T7" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D7),COUNTIF($F$4:F6,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F6,T$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$13=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D7),COUNTIF($F$4:F6,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F6,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F6,T$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$13=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F6,T$3)=1,AND(COUNTIF($F$4:F6,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F6,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F6,T$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U7" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A7=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D7),COUNTIF($F$4:F6,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F6,U$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$14=$C7,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C7=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D7),COUNTIF($F$4:F6,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F6,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F6,U$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$14=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F6,U$3)=1,AND(COUNTIF($F$4:F6,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F6,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F6,U$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V7" s="74" t="n">
         <x:f>IF($A7="","",IF($J7="人数希望一致",1,0))</x:f>
@@ -2295,7 +2440,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F8" s="74" t="str">
-        <x:f>IF($A8="","",IF(MAX(L8:U8)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L8:U8),L8:U8,0))))</x:f>
+        <x:f>IF($A8="","",IF(COUNTIF(L8:U8,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L8:U8),L8:U8,0))))</x:f>
         <x:v>cad_tanaka</x:v>
       </x:c>
       <x:c r="G8" s="74" t="str">
@@ -2311,46 +2456,46 @@
         <x:v>46270.791666666664</x:v>
       </x:c>
       <x:c r="J8" s="85" t="str">
-        <x:f>IF($A8="","",IF($F8="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F8,'キャディ条件'!$A$5:$A$14,0))=$C8,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F8,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A8="","",IF($F8="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F8,'キャディ条件'!$A$5:$A$14,0))=$C8,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F8,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F8)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
         <x:v>2ラウンド希望を考慮</x:v>
       </x:c>
       <x:c r="K8" s="85" t="str">
         <x:f>IF($A8="","",IF($F8="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L8" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D8),COUNTIF($F$4:F7,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F7,L$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$5=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D8),COUNTIF($F$4:F7,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F7,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F7,L$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$5=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F7,L$3)=1,AND(COUNTIF($F$4:F7,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F7,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F7,L$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="M8" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D8),COUNTIF($F$4:F7,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F7,M$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$6=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D8),COUNTIF($F$4:F7,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F7,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F7,M$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$6=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F7,M$3)=1,AND(COUNTIF($F$4:F7,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F7,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F7,M$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="N8" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D8),COUNTIF($F$4:F7,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F7,N$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$7=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>127</x:v>
+        <x:f>IF(OR(N$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D8),COUNTIF($F$4:F7,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F7,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F7,N$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$7=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F7,N$3)=1,AND(COUNTIF($F$4:F7,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F7,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F7,N$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="O8" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D8),COUNTIF($F$4:F7,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F7,O$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$8=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D8),COUNTIF($F$4:F7,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F7,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F7,O$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$8=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F7,O$3)=1,AND(COUNTIF($F$4:F7,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F7,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F7,O$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="P8" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D8),COUNTIF($F$4:F7,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F7,P$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$9=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D8),COUNTIF($F$4:F7,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F7,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F7,P$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$9=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F7,P$3)=1,AND(COUNTIF($F$4:F7,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F7,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F7,P$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q8" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D8),COUNTIF($F$4:F7,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F7,Q$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$10=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D8),COUNTIF($F$4:F7,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F7,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F7,Q$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$10=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F7,Q$3)=1,AND(COUNTIF($F$4:F7,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F7,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F7,Q$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R8" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D8),COUNTIF($F$4:F7,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F7,R$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$11=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D8),COUNTIF($F$4:F7,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F7,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F7,R$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$11=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F7,R$3)=1,AND(COUNTIF($F$4:F7,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F7,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F7,R$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S8" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D8),COUNTIF($F$4:F7,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F7,S$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$12=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D8),COUNTIF($F$4:F7,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F7,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F7,S$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$12=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F7,S$3)=1,AND(COUNTIF($F$4:F7,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F7,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F7,S$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T8" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D8),COUNTIF($F$4:F7,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F7,T$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$13=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D8),COUNTIF($F$4:F7,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F7,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F7,T$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$13=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F7,T$3)=1,AND(COUNTIF($F$4:F7,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F7,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F7,T$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U8" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A8=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D8),COUNTIF($F$4:F7,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F7,U$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$14=$C8,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C8=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D8),COUNTIF($F$4:F7,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F7,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F7,U$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$14=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F7,U$3)=1,AND(COUNTIF($F$4:F7,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F7,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F7,U$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V8" s="74" t="n">
         <x:f>IF($A8="","",IF($J8="人数希望一致",1,0))</x:f>
@@ -2379,7 +2524,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F9" s="74" t="str">
-        <x:f>IF($A9="","",IF(MAX(L9:U9)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L9:U9),L9:U9,0))))</x:f>
+        <x:f>IF($A9="","",IF(COUNTIF(L9:U9,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L9:U9),L9:U9,0))))</x:f>
         <x:v>cad_ito</x:v>
       </x:c>
       <x:c r="G9" s="74" t="str">
@@ -2395,46 +2540,46 @@
         <x:v>46270.8125</x:v>
       </x:c>
       <x:c r="J9" s="85" t="str">
-        <x:f>IF($A9="","",IF($F9="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F9,'キャディ条件'!$A$5:$A$14,0))=$C9,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F9,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A9="","",IF($F9="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F9,'キャディ条件'!$A$5:$A$14,0))=$C9,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F9,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F9)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
         <x:v>公平性・残容量</x:v>
       </x:c>
       <x:c r="K9" s="85" t="str">
         <x:f>IF($A9="","",IF($F9="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L9" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D9),COUNTIF($F$4:F8,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F8,L$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$5=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D9),COUNTIF($F$4:F8,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F8,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F8,L$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$5=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F8,L$3)=1,AND(COUNTIF($F$4:F8,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F8,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F8,L$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="M9" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D9),COUNTIF($F$4:F8,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F8,M$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$6=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D9),COUNTIF($F$4:F8,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F8,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F8,M$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$6=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F8,M$3)=1,AND(COUNTIF($F$4:F8,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F8,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F8,M$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="N9" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D9),COUNTIF($F$4:F8,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F8,N$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$7=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D9),COUNTIF($F$4:F8,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F8,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F8,N$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$7=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F8,N$3)=1,AND(COUNTIF($F$4:F8,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F8,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F8,N$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="O9" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D9),COUNTIF($F$4:F8,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F8,O$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$8=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D9),COUNTIF($F$4:F8,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F8,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F8,O$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$8=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F8,O$3)=1,AND(COUNTIF($F$4:F8,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F8,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F8,O$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>-9999</x:v>
       </x:c>
       <x:c r="P9" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D9),COUNTIF($F$4:F8,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F8,P$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$9=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D9),COUNTIF($F$4:F8,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F8,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F8,P$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$9=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F8,P$3)=1,AND(COUNTIF($F$4:F8,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F8,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F8,P$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q9" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D9),COUNTIF($F$4:F8,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F8,Q$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$10=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D9),COUNTIF($F$4:F8,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F8,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F8,Q$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$10=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F8,Q$3)=1,AND(COUNTIF($F$4:F8,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F8,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F8,Q$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R9" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D9),COUNTIF($F$4:F8,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F8,R$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$11=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D9),COUNTIF($F$4:F8,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F8,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F8,R$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$11=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F8,R$3)=1,AND(COUNTIF($F$4:F8,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F8,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F8,R$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S9" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D9),COUNTIF($F$4:F8,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F8,S$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$12=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D9),COUNTIF($F$4:F8,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F8,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F8,S$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$12=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F8,S$3)=1,AND(COUNTIF($F$4:F8,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F8,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F8,S$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T9" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D9),COUNTIF($F$4:F8,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F8,T$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$13=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D9),COUNTIF($F$4:F8,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F8,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F8,T$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$13=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F8,T$3)=1,AND(COUNTIF($F$4:F8,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F8,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F8,T$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U9" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A9=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D9),COUNTIF($F$4:F8,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F8,U$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$14=$C9,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C9=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D9),COUNTIF($F$4:F8,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F8,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F8,U$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$14=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F8,U$3)=1,AND(COUNTIF($F$4:F8,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F8,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F8,U$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V9" s="74" t="n">
         <x:f>IF($A9="","",IF($J9="人数希望一致",1,0))</x:f>
@@ -2458,7 +2603,7 @@
         <x:f>IF('ラウンド入力'!A10="","",IF('ラウンド入力'!E10="",'設定・説明'!$B$6,'ラウンド入力'!E10))</x:f>
       </x:c>
       <x:c r="F10" s="74" t="str">
-        <x:f>IF($A10="","",IF(MAX(L10:U10)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L10:U10),L10:U10,0))))</x:f>
+        <x:f>IF($A10="","",IF(COUNTIF(L10:U10,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L10:U10),L10:U10,0))))</x:f>
       </x:c>
       <x:c r="G10" s="74" t="str">
         <x:f>IF(OR($F10="",$F10="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F10,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2470,40 +2615,40 @@
         <x:f>IF($A10="","",$H10+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J10" s="85" t="str">
-        <x:f>IF($A10="","",IF($F10="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F10,'キャディ条件'!$A$5:$A$14,0))=$C10,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F10,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A10="","",IF($F10="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F10,'キャディ条件'!$A$5:$A$14,0))=$C10,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F10,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F10)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K10" s="85" t="str">
         <x:f>IF($A10="","",IF($F10="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L10" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D10),COUNTIF($F$4:F9,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F9,L$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$5=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D10),COUNTIF($F$4:F9,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F9,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F9,L$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$5=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F9,L$3)=1,AND(COUNTIF($F$4:F9,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F9,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F9,L$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M10" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D10),COUNTIF($F$4:F9,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F9,M$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$6=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D10),COUNTIF($F$4:F9,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F9,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F9,M$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$6=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F9,M$3)=1,AND(COUNTIF($F$4:F9,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F9,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F9,M$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N10" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D10),COUNTIF($F$4:F9,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F9,N$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$7=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D10),COUNTIF($F$4:F9,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F9,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F9,N$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$7=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F9,N$3)=1,AND(COUNTIF($F$4:F9,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F9,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F9,N$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O10" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D10),COUNTIF($F$4:F9,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F9,O$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$8=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D10),COUNTIF($F$4:F9,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F9,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F9,O$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$8=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F9,O$3)=1,AND(COUNTIF($F$4:F9,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F9,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F9,O$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P10" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D10),COUNTIF($F$4:F9,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F9,P$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$9=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D10),COUNTIF($F$4:F9,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F9,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F9,P$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$9=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F9,P$3)=1,AND(COUNTIF($F$4:F9,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F9,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F9,P$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q10" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D10),COUNTIF($F$4:F9,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F9,Q$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$10=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D10),COUNTIF($F$4:F9,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F9,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F9,Q$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$10=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F9,Q$3)=1,AND(COUNTIF($F$4:F9,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F9,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F9,Q$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R10" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D10),COUNTIF($F$4:F9,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F9,R$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$11=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D10),COUNTIF($F$4:F9,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F9,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F9,R$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$11=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F9,R$3)=1,AND(COUNTIF($F$4:F9,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F9,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F9,R$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S10" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D10),COUNTIF($F$4:F9,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F9,S$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$12=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D10),COUNTIF($F$4:F9,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F9,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F9,S$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$12=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F9,S$3)=1,AND(COUNTIF($F$4:F9,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F9,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F9,S$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T10" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D10),COUNTIF($F$4:F9,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F9,T$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$13=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D10),COUNTIF($F$4:F9,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F9,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F9,T$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$13=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F9,T$3)=1,AND(COUNTIF($F$4:F9,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F9,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F9,T$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U10" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A10=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D10),COUNTIF($F$4:F9,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F9,U$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$14=$C10,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C10=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D10),COUNTIF($F$4:F9,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F9,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F9,U$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$14=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F9,U$3)=1,AND(COUNTIF($F$4:F9,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F9,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F9,U$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V10" s="74" t="str">
         <x:f>IF($A10="","",IF($J10="人数希望一致",1,0))</x:f>
@@ -2526,7 +2671,7 @@
         <x:f>IF('ラウンド入力'!A11="","",IF('ラウンド入力'!E11="",'設定・説明'!$B$6,'ラウンド入力'!E11))</x:f>
       </x:c>
       <x:c r="F11" s="74" t="str">
-        <x:f>IF($A11="","",IF(MAX(L11:U11)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L11:U11),L11:U11,0))))</x:f>
+        <x:f>IF($A11="","",IF(COUNTIF(L11:U11,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L11:U11),L11:U11,0))))</x:f>
       </x:c>
       <x:c r="G11" s="74" t="str">
         <x:f>IF(OR($F11="",$F11="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F11,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2538,40 +2683,40 @@
         <x:f>IF($A11="","",$H11+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J11" s="85" t="str">
-        <x:f>IF($A11="","",IF($F11="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F11,'キャディ条件'!$A$5:$A$14,0))=$C11,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F11,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A11="","",IF($F11="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F11,'キャディ条件'!$A$5:$A$14,0))=$C11,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F11,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F11)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K11" s="85" t="str">
         <x:f>IF($A11="","",IF($F11="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L11" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D11),COUNTIF($F$4:F10,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F10,L$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$5=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D11),COUNTIF($F$4:F10,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F10,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F10,L$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$5=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F10,L$3)=1,AND(COUNTIF($F$4:F10,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F10,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F10,L$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M11" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D11),COUNTIF($F$4:F10,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F10,M$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$6=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D11),COUNTIF($F$4:F10,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F10,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F10,M$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$6=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F10,M$3)=1,AND(COUNTIF($F$4:F10,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F10,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F10,M$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N11" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D11),COUNTIF($F$4:F10,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F10,N$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$7=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D11),COUNTIF($F$4:F10,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F10,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F10,N$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$7=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F10,N$3)=1,AND(COUNTIF($F$4:F10,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F10,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F10,N$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O11" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D11),COUNTIF($F$4:F10,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F10,O$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$8=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D11),COUNTIF($F$4:F10,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F10,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F10,O$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$8=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F10,O$3)=1,AND(COUNTIF($F$4:F10,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F10,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F10,O$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P11" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D11),COUNTIF($F$4:F10,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F10,P$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$9=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D11),COUNTIF($F$4:F10,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F10,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F10,P$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$9=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F10,P$3)=1,AND(COUNTIF($F$4:F10,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F10,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F10,P$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q11" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D11),COUNTIF($F$4:F10,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F10,Q$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$10=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D11),COUNTIF($F$4:F10,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F10,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F10,Q$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$10=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F10,Q$3)=1,AND(COUNTIF($F$4:F10,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F10,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F10,Q$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R11" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D11),COUNTIF($F$4:F10,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F10,R$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$11=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D11),COUNTIF($F$4:F10,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F10,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F10,R$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$11=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F10,R$3)=1,AND(COUNTIF($F$4:F10,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F10,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F10,R$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S11" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D11),COUNTIF($F$4:F10,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F10,S$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$12=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D11),COUNTIF($F$4:F10,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F10,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F10,S$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$12=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F10,S$3)=1,AND(COUNTIF($F$4:F10,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F10,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F10,S$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T11" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D11),COUNTIF($F$4:F10,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F10,T$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$13=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D11),COUNTIF($F$4:F10,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F10,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F10,T$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$13=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F10,T$3)=1,AND(COUNTIF($F$4:F10,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F10,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F10,T$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U11" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A11=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D11),COUNTIF($F$4:F10,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F10,U$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$14=$C11,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C11=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D11),COUNTIF($F$4:F10,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F10,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F10,U$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$14=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F10,U$3)=1,AND(COUNTIF($F$4:F10,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F10,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F10,U$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V11" s="74" t="str">
         <x:f>IF($A11="","",IF($J11="人数希望一致",1,0))</x:f>
@@ -2594,7 +2739,7 @@
         <x:f>IF('ラウンド入力'!A12="","",IF('ラウンド入力'!E12="",'設定・説明'!$B$6,'ラウンド入力'!E12))</x:f>
       </x:c>
       <x:c r="F12" s="74" t="str">
-        <x:f>IF($A12="","",IF(MAX(L12:U12)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L12:U12),L12:U12,0))))</x:f>
+        <x:f>IF($A12="","",IF(COUNTIF(L12:U12,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L12:U12),L12:U12,0))))</x:f>
       </x:c>
       <x:c r="G12" s="74" t="str">
         <x:f>IF(OR($F12="",$F12="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F12,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2606,40 +2751,40 @@
         <x:f>IF($A12="","",$H12+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J12" s="85" t="str">
-        <x:f>IF($A12="","",IF($F12="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F12,'キャディ条件'!$A$5:$A$14,0))=$C12,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F12,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A12="","",IF($F12="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F12,'キャディ条件'!$A$5:$A$14,0))=$C12,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F12,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F12)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K12" s="85" t="str">
         <x:f>IF($A12="","",IF($F12="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L12" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D12),COUNTIF($F$4:F11,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F11,L$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$5=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D12),COUNTIF($F$4:F11,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F11,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F11,L$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$5=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F11,L$3)=1,AND(COUNTIF($F$4:F11,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F11,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F11,L$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M12" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D12),COUNTIF($F$4:F11,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F11,M$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$6=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D12),COUNTIF($F$4:F11,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F11,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F11,M$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$6=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F11,M$3)=1,AND(COUNTIF($F$4:F11,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F11,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F11,M$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N12" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D12),COUNTIF($F$4:F11,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F11,N$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$7=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D12),COUNTIF($F$4:F11,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F11,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F11,N$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$7=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F11,N$3)=1,AND(COUNTIF($F$4:F11,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F11,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F11,N$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O12" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D12),COUNTIF($F$4:F11,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F11,O$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$8=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D12),COUNTIF($F$4:F11,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F11,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F11,O$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$8=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F11,O$3)=1,AND(COUNTIF($F$4:F11,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F11,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F11,O$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P12" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D12),COUNTIF($F$4:F11,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F11,P$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$9=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D12),COUNTIF($F$4:F11,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F11,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F11,P$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$9=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F11,P$3)=1,AND(COUNTIF($F$4:F11,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F11,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F11,P$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q12" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D12),COUNTIF($F$4:F11,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F11,Q$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$10=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D12),COUNTIF($F$4:F11,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F11,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F11,Q$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$10=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F11,Q$3)=1,AND(COUNTIF($F$4:F11,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F11,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F11,Q$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R12" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D12),COUNTIF($F$4:F11,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F11,R$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$11=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D12),COUNTIF($F$4:F11,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F11,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F11,R$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$11=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F11,R$3)=1,AND(COUNTIF($F$4:F11,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F11,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F11,R$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S12" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D12),COUNTIF($F$4:F11,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F11,S$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$12=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D12),COUNTIF($F$4:F11,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F11,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F11,S$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$12=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F11,S$3)=1,AND(COUNTIF($F$4:F11,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F11,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F11,S$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T12" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D12),COUNTIF($F$4:F11,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F11,T$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$13=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D12),COUNTIF($F$4:F11,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F11,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F11,T$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$13=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F11,T$3)=1,AND(COUNTIF($F$4:F11,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F11,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F11,T$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U12" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A12=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D12),COUNTIF($F$4:F11,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F11,U$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$14=$C12,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C12=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D12),COUNTIF($F$4:F11,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F11,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F11,U$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$14=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F11,U$3)=1,AND(COUNTIF($F$4:F11,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F11,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F11,U$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V12" s="74" t="str">
         <x:f>IF($A12="","",IF($J12="人数希望一致",1,0))</x:f>
@@ -2662,7 +2807,7 @@
         <x:f>IF('ラウンド入力'!A13="","",IF('ラウンド入力'!E13="",'設定・説明'!$B$6,'ラウンド入力'!E13))</x:f>
       </x:c>
       <x:c r="F13" s="74" t="str">
-        <x:f>IF($A13="","",IF(MAX(L13:U13)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L13:U13),L13:U13,0))))</x:f>
+        <x:f>IF($A13="","",IF(COUNTIF(L13:U13,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L13:U13),L13:U13,0))))</x:f>
       </x:c>
       <x:c r="G13" s="74" t="str">
         <x:f>IF(OR($F13="",$F13="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F13,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2674,40 +2819,40 @@
         <x:f>IF($A13="","",$H13+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J13" s="85" t="str">
-        <x:f>IF($A13="","",IF($F13="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F13,'キャディ条件'!$A$5:$A$14,0))=$C13,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F13,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A13="","",IF($F13="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F13,'キャディ条件'!$A$5:$A$14,0))=$C13,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F13,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F13)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K13" s="85" t="str">
         <x:f>IF($A13="","",IF($F13="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L13" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D13),COUNTIF($F$4:F12,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F12,L$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$5=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D13),COUNTIF($F$4:F12,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F12,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F12,L$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$5=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F12,L$3)=1,AND(COUNTIF($F$4:F12,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F12,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F12,L$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M13" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D13),COUNTIF($F$4:F12,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F12,M$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$6=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D13),COUNTIF($F$4:F12,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F12,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F12,M$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$6=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F12,M$3)=1,AND(COUNTIF($F$4:F12,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F12,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F12,M$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N13" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D13),COUNTIF($F$4:F12,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F12,N$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$7=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D13),COUNTIF($F$4:F12,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F12,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F12,N$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$7=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F12,N$3)=1,AND(COUNTIF($F$4:F12,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F12,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F12,N$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O13" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D13),COUNTIF($F$4:F12,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F12,O$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$8=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D13),COUNTIF($F$4:F12,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F12,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F12,O$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$8=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F12,O$3)=1,AND(COUNTIF($F$4:F12,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F12,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F12,O$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P13" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D13),COUNTIF($F$4:F12,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F12,P$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$9=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D13),COUNTIF($F$4:F12,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F12,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F12,P$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$9=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F12,P$3)=1,AND(COUNTIF($F$4:F12,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F12,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F12,P$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q13" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D13),COUNTIF($F$4:F12,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F12,Q$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$10=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D13),COUNTIF($F$4:F12,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F12,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F12,Q$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$10=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F12,Q$3)=1,AND(COUNTIF($F$4:F12,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F12,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F12,Q$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R13" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D13),COUNTIF($F$4:F12,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F12,R$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$11=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D13),COUNTIF($F$4:F12,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F12,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F12,R$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$11=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F12,R$3)=1,AND(COUNTIF($F$4:F12,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F12,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F12,R$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S13" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D13),COUNTIF($F$4:F12,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F12,S$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$12=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D13),COUNTIF($F$4:F12,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F12,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F12,S$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$12=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F12,S$3)=1,AND(COUNTIF($F$4:F12,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F12,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F12,S$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T13" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D13),COUNTIF($F$4:F12,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F12,T$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$13=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D13),COUNTIF($F$4:F12,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F12,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F12,T$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$13=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F12,T$3)=1,AND(COUNTIF($F$4:F12,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F12,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F12,T$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U13" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A13=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D13),COUNTIF($F$4:F12,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F12,U$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$14=$C13,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C13=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D13),COUNTIF($F$4:F12,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F12,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F12,U$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$14=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F12,U$3)=1,AND(COUNTIF($F$4:F12,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F12,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F12,U$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V13" s="74" t="str">
         <x:f>IF($A13="","",IF($J13="人数希望一致",1,0))</x:f>
@@ -2730,7 +2875,7 @@
         <x:f>IF('ラウンド入力'!A14="","",IF('ラウンド入力'!E14="",'設定・説明'!$B$6,'ラウンド入力'!E14))</x:f>
       </x:c>
       <x:c r="F14" s="74" t="str">
-        <x:f>IF($A14="","",IF(MAX(L14:U14)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L14:U14),L14:U14,0))))</x:f>
+        <x:f>IF($A14="","",IF(COUNTIF(L14:U14,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L14:U14),L14:U14,0))))</x:f>
       </x:c>
       <x:c r="G14" s="74" t="str">
         <x:f>IF(OR($F14="",$F14="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F14,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2742,40 +2887,40 @@
         <x:f>IF($A14="","",$H14+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J14" s="85" t="str">
-        <x:f>IF($A14="","",IF($F14="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F14,'キャディ条件'!$A$5:$A$14,0))=$C14,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F14,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A14="","",IF($F14="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F14,'キャディ条件'!$A$5:$A$14,0))=$C14,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F14,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F14)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K14" s="85" t="str">
         <x:f>IF($A14="","",IF($F14="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L14" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D14),COUNTIF($F$4:F13,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F13,L$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$5=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D14),COUNTIF($F$4:F13,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F13,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F13,L$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$5=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F13,L$3)=1,AND(COUNTIF($F$4:F13,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F13,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F13,L$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M14" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D14),COUNTIF($F$4:F13,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F13,M$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$6=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D14),COUNTIF($F$4:F13,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F13,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F13,M$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$6=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F13,M$3)=1,AND(COUNTIF($F$4:F13,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F13,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F13,M$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N14" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D14),COUNTIF($F$4:F13,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F13,N$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$7=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D14),COUNTIF($F$4:F13,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F13,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F13,N$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$7=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F13,N$3)=1,AND(COUNTIF($F$4:F13,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F13,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F13,N$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O14" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D14),COUNTIF($F$4:F13,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F13,O$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$8=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D14),COUNTIF($F$4:F13,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F13,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F13,O$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$8=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F13,O$3)=1,AND(COUNTIF($F$4:F13,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F13,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F13,O$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P14" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D14),COUNTIF($F$4:F13,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F13,P$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$9=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D14),COUNTIF($F$4:F13,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F13,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F13,P$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$9=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F13,P$3)=1,AND(COUNTIF($F$4:F13,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F13,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F13,P$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q14" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D14),COUNTIF($F$4:F13,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F13,Q$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$10=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D14),COUNTIF($F$4:F13,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F13,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F13,Q$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$10=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F13,Q$3)=1,AND(COUNTIF($F$4:F13,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F13,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F13,Q$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R14" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D14),COUNTIF($F$4:F13,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F13,R$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$11=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D14),COUNTIF($F$4:F13,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F13,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F13,R$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$11=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F13,R$3)=1,AND(COUNTIF($F$4:F13,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F13,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F13,R$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S14" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D14),COUNTIF($F$4:F13,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F13,S$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$12=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D14),COUNTIF($F$4:F13,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F13,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F13,S$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$12=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F13,S$3)=1,AND(COUNTIF($F$4:F13,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F13,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F13,S$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T14" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D14),COUNTIF($F$4:F13,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F13,T$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$13=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D14),COUNTIF($F$4:F13,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F13,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F13,T$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$13=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F13,T$3)=1,AND(COUNTIF($F$4:F13,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F13,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F13,T$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U14" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A14=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D14),COUNTIF($F$4:F13,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F13,U$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$14=$C14,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C14=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D14),COUNTIF($F$4:F13,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F13,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F13,U$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$14=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F13,U$3)=1,AND(COUNTIF($F$4:F13,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F13,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F13,U$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V14" s="74" t="str">
         <x:f>IF($A14="","",IF($J14="人数希望一致",1,0))</x:f>
@@ -2798,7 +2943,7 @@
         <x:f>IF('ラウンド入力'!A15="","",IF('ラウンド入力'!E15="",'設定・説明'!$B$6,'ラウンド入力'!E15))</x:f>
       </x:c>
       <x:c r="F15" s="74" t="str">
-        <x:f>IF($A15="","",IF(MAX(L15:U15)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L15:U15),L15:U15,0))))</x:f>
+        <x:f>IF($A15="","",IF(COUNTIF(L15:U15,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L15:U15),L15:U15,0))))</x:f>
       </x:c>
       <x:c r="G15" s="74" t="str">
         <x:f>IF(OR($F15="",$F15="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F15,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2810,40 +2955,40 @@
         <x:f>IF($A15="","",$H15+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J15" s="85" t="str">
-        <x:f>IF($A15="","",IF($F15="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F15,'キャディ条件'!$A$5:$A$14,0))=$C15,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F15,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A15="","",IF($F15="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F15,'キャディ条件'!$A$5:$A$14,0))=$C15,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F15,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F15)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K15" s="85" t="str">
         <x:f>IF($A15="","",IF($F15="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L15" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D15),COUNTIF($F$4:F14,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F14,L$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$5=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D15),COUNTIF($F$4:F14,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F14,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F14,L$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$5=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F14,L$3)=1,AND(COUNTIF($F$4:F14,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F14,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F14,L$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M15" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D15),COUNTIF($F$4:F14,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F14,M$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$6=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D15),COUNTIF($F$4:F14,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F14,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F14,M$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$6=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F14,M$3)=1,AND(COUNTIF($F$4:F14,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F14,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F14,M$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N15" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D15),COUNTIF($F$4:F14,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F14,N$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$7=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D15),COUNTIF($F$4:F14,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F14,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F14,N$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$7=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F14,N$3)=1,AND(COUNTIF($F$4:F14,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F14,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F14,N$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O15" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D15),COUNTIF($F$4:F14,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F14,O$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$8=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D15),COUNTIF($F$4:F14,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F14,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F14,O$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$8=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F14,O$3)=1,AND(COUNTIF($F$4:F14,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F14,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F14,O$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P15" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D15),COUNTIF($F$4:F14,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F14,P$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$9=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D15),COUNTIF($F$4:F14,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F14,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F14,P$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$9=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F14,P$3)=1,AND(COUNTIF($F$4:F14,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F14,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F14,P$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q15" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D15),COUNTIF($F$4:F14,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F14,Q$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$10=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D15),COUNTIF($F$4:F14,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F14,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F14,Q$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$10=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F14,Q$3)=1,AND(COUNTIF($F$4:F14,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F14,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F14,Q$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R15" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D15),COUNTIF($F$4:F14,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F14,R$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$11=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D15),COUNTIF($F$4:F14,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F14,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F14,R$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$11=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F14,R$3)=1,AND(COUNTIF($F$4:F14,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F14,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F14,R$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S15" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D15),COUNTIF($F$4:F14,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F14,S$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$12=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D15),COUNTIF($F$4:F14,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F14,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F14,S$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$12=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F14,S$3)=1,AND(COUNTIF($F$4:F14,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F14,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F14,S$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T15" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D15),COUNTIF($F$4:F14,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F14,T$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$13=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D15),COUNTIF($F$4:F14,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F14,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F14,T$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$13=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F14,T$3)=1,AND(COUNTIF($F$4:F14,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F14,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F14,T$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U15" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A15=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D15),COUNTIF($F$4:F14,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F14,U$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$14=$C15,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C15=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D15),COUNTIF($F$4:F14,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F14,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F14,U$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$14=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F14,U$3)=1,AND(COUNTIF($F$4:F14,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F14,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F14,U$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V15" s="74" t="str">
         <x:f>IF($A15="","",IF($J15="人数希望一致",1,0))</x:f>
@@ -2866,7 +3011,7 @@
         <x:f>IF('ラウンド入力'!A16="","",IF('ラウンド入力'!E16="",'設定・説明'!$B$6,'ラウンド入力'!E16))</x:f>
       </x:c>
       <x:c r="F16" s="74" t="str">
-        <x:f>IF($A16="","",IF(MAX(L16:U16)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L16:U16),L16:U16,0))))</x:f>
+        <x:f>IF($A16="","",IF(COUNTIF(L16:U16,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L16:U16),L16:U16,0))))</x:f>
       </x:c>
       <x:c r="G16" s="74" t="str">
         <x:f>IF(OR($F16="",$F16="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F16,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2878,40 +3023,40 @@
         <x:f>IF($A16="","",$H16+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J16" s="85" t="str">
-        <x:f>IF($A16="","",IF($F16="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F16,'キャディ条件'!$A$5:$A$14,0))=$C16,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F16,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A16="","",IF($F16="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F16,'キャディ条件'!$A$5:$A$14,0))=$C16,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F16,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F16)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K16" s="85" t="str">
         <x:f>IF($A16="","",IF($F16="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L16" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D16),COUNTIF($F$4:F15,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F15,L$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$5=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D16),COUNTIF($F$4:F15,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F15,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F15,L$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$5=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F15,L$3)=1,AND(COUNTIF($F$4:F15,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F15,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F15,L$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M16" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D16),COUNTIF($F$4:F15,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F15,M$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$6=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D16),COUNTIF($F$4:F15,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F15,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F15,M$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$6=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F15,M$3)=1,AND(COUNTIF($F$4:F15,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F15,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F15,M$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N16" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D16),COUNTIF($F$4:F15,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F15,N$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$7=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D16),COUNTIF($F$4:F15,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F15,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F15,N$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$7=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F15,N$3)=1,AND(COUNTIF($F$4:F15,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F15,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F15,N$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O16" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D16),COUNTIF($F$4:F15,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F15,O$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$8=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D16),COUNTIF($F$4:F15,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F15,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F15,O$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$8=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F15,O$3)=1,AND(COUNTIF($F$4:F15,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F15,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F15,O$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P16" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D16),COUNTIF($F$4:F15,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F15,P$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$9=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D16),COUNTIF($F$4:F15,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F15,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F15,P$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$9=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F15,P$3)=1,AND(COUNTIF($F$4:F15,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F15,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F15,P$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q16" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D16),COUNTIF($F$4:F15,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F15,Q$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$10=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D16),COUNTIF($F$4:F15,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F15,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F15,Q$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$10=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F15,Q$3)=1,AND(COUNTIF($F$4:F15,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F15,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F15,Q$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R16" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D16),COUNTIF($F$4:F15,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F15,R$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$11=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D16),COUNTIF($F$4:F15,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F15,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F15,R$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$11=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F15,R$3)=1,AND(COUNTIF($F$4:F15,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F15,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F15,R$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S16" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D16),COUNTIF($F$4:F15,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F15,S$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$12=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D16),COUNTIF($F$4:F15,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F15,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F15,S$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$12=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F15,S$3)=1,AND(COUNTIF($F$4:F15,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F15,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F15,S$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T16" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D16),COUNTIF($F$4:F15,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F15,T$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$13=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D16),COUNTIF($F$4:F15,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F15,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F15,T$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$13=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F15,T$3)=1,AND(COUNTIF($F$4:F15,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F15,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F15,T$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U16" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A16=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D16),COUNTIF($F$4:F15,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F15,U$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$14=$C16,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C16=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D16),COUNTIF($F$4:F15,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F15,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F15,U$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$14=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F15,U$3)=1,AND(COUNTIF($F$4:F15,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F15,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F15,U$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V16" s="74" t="str">
         <x:f>IF($A16="","",IF($J16="人数希望一致",1,0))</x:f>
@@ -2934,7 +3079,7 @@
         <x:f>IF('ラウンド入力'!A17="","",IF('ラウンド入力'!E17="",'設定・説明'!$B$6,'ラウンド入力'!E17))</x:f>
       </x:c>
       <x:c r="F17" s="74" t="str">
-        <x:f>IF($A17="","",IF(MAX(L17:U17)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L17:U17),L17:U17,0))))</x:f>
+        <x:f>IF($A17="","",IF(COUNTIF(L17:U17,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L17:U17),L17:U17,0))))</x:f>
       </x:c>
       <x:c r="G17" s="74" t="str">
         <x:f>IF(OR($F17="",$F17="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F17,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2946,40 +3091,40 @@
         <x:f>IF($A17="","",$H17+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J17" s="85" t="str">
-        <x:f>IF($A17="","",IF($F17="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F17,'キャディ条件'!$A$5:$A$14,0))=$C17,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F17,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A17="","",IF($F17="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F17,'キャディ条件'!$A$5:$A$14,0))=$C17,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F17,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F17)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K17" s="85" t="str">
         <x:f>IF($A17="","",IF($F17="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L17" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D17),COUNTIF($F$4:F16,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F16,L$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$5=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D17),COUNTIF($F$4:F16,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F16,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F16,L$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$5=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F16,L$3)=1,AND(COUNTIF($F$4:F16,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F16,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F16,L$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M17" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D17),COUNTIF($F$4:F16,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F16,M$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$6=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D17),COUNTIF($F$4:F16,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F16,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F16,M$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$6=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F16,M$3)=1,AND(COUNTIF($F$4:F16,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F16,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F16,M$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N17" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D17),COUNTIF($F$4:F16,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F16,N$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$7=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D17),COUNTIF($F$4:F16,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F16,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F16,N$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$7=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F16,N$3)=1,AND(COUNTIF($F$4:F16,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F16,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F16,N$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O17" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D17),COUNTIF($F$4:F16,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F16,O$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$8=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D17),COUNTIF($F$4:F16,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F16,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F16,O$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$8=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F16,O$3)=1,AND(COUNTIF($F$4:F16,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F16,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F16,O$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P17" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D17),COUNTIF($F$4:F16,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F16,P$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$9=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D17),COUNTIF($F$4:F16,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F16,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F16,P$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$9=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F16,P$3)=1,AND(COUNTIF($F$4:F16,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F16,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F16,P$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q17" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D17),COUNTIF($F$4:F16,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F16,Q$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$10=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D17),COUNTIF($F$4:F16,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F16,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F16,Q$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$10=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F16,Q$3)=1,AND(COUNTIF($F$4:F16,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F16,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F16,Q$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R17" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D17),COUNTIF($F$4:F16,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F16,R$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$11=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D17),COUNTIF($F$4:F16,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F16,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F16,R$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$11=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F16,R$3)=1,AND(COUNTIF($F$4:F16,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F16,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F16,R$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S17" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D17),COUNTIF($F$4:F16,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F16,S$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$12=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D17),COUNTIF($F$4:F16,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F16,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F16,S$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$12=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F16,S$3)=1,AND(COUNTIF($F$4:F16,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F16,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F16,S$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T17" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D17),COUNTIF($F$4:F16,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F16,T$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$13=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D17),COUNTIF($F$4:F16,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F16,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F16,T$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$13=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F16,T$3)=1,AND(COUNTIF($F$4:F16,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F16,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F16,T$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U17" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A17=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D17),COUNTIF($F$4:F16,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F16,U$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$14=$C17,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C17=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D17),COUNTIF($F$4:F16,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F16,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F16,U$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$14=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F16,U$3)=1,AND(COUNTIF($F$4:F16,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F16,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F16,U$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V17" s="74" t="str">
         <x:f>IF($A17="","",IF($J17="人数希望一致",1,0))</x:f>
@@ -3002,7 +3147,7 @@
         <x:f>IF('ラウンド入力'!A18="","",IF('ラウンド入力'!E18="",'設定・説明'!$B$6,'ラウンド入力'!E18))</x:f>
       </x:c>
       <x:c r="F18" s="74" t="str">
-        <x:f>IF($A18="","",IF(MAX(L18:U18)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L18:U18),L18:U18,0))))</x:f>
+        <x:f>IF($A18="","",IF(COUNTIF(L18:U18,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L18:U18),L18:U18,0))))</x:f>
       </x:c>
       <x:c r="G18" s="74" t="str">
         <x:f>IF(OR($F18="",$F18="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F18,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -3014,40 +3159,40 @@
         <x:f>IF($A18="","",$H18+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J18" s="85" t="str">
-        <x:f>IF($A18="","",IF($F18="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F18,'キャディ条件'!$A$5:$A$14,0))=$C18,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F18,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A18="","",IF($F18="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F18,'キャディ条件'!$A$5:$A$14,0))=$C18,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F18,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F18)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K18" s="85" t="str">
         <x:f>IF($A18="","",IF($F18="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L18" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D18),COUNTIF($F$4:F17,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F17,L$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$5=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D18),COUNTIF($F$4:F17,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F17,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F17,L$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$5=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F17,L$3)=1,AND(COUNTIF($F$4:F17,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F17,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F17,L$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M18" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D18),COUNTIF($F$4:F17,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F17,M$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$6=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D18),COUNTIF($F$4:F17,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F17,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F17,M$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$6=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F17,M$3)=1,AND(COUNTIF($F$4:F17,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F17,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F17,M$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N18" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D18),COUNTIF($F$4:F17,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F17,N$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$7=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D18),COUNTIF($F$4:F17,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F17,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F17,N$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$7=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F17,N$3)=1,AND(COUNTIF($F$4:F17,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F17,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F17,N$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O18" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D18),COUNTIF($F$4:F17,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F17,O$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$8=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D18),COUNTIF($F$4:F17,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F17,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F17,O$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$8=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F17,O$3)=1,AND(COUNTIF($F$4:F17,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F17,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F17,O$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P18" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D18),COUNTIF($F$4:F17,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F17,P$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$9=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D18),COUNTIF($F$4:F17,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F17,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F17,P$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$9=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F17,P$3)=1,AND(COUNTIF($F$4:F17,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F17,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F17,P$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q18" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D18),COUNTIF($F$4:F17,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F17,Q$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$10=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D18),COUNTIF($F$4:F17,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F17,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F17,Q$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$10=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F17,Q$3)=1,AND(COUNTIF($F$4:F17,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F17,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F17,Q$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R18" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D18),COUNTIF($F$4:F17,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F17,R$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$11=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D18),COUNTIF($F$4:F17,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F17,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F17,R$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$11=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F17,R$3)=1,AND(COUNTIF($F$4:F17,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F17,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F17,R$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S18" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D18),COUNTIF($F$4:F17,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F17,S$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$12=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D18),COUNTIF($F$4:F17,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F17,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F17,S$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$12=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F17,S$3)=1,AND(COUNTIF($F$4:F17,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F17,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F17,S$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T18" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D18),COUNTIF($F$4:F17,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F17,T$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$13=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D18),COUNTIF($F$4:F17,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F17,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F17,T$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$13=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F17,T$3)=1,AND(COUNTIF($F$4:F17,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F17,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F17,T$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U18" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A18=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D18),COUNTIF($F$4:F17,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F17,U$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$14=$C18,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C18=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D18),COUNTIF($F$4:F17,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F17,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F17,U$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$14=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F17,U$3)=1,AND(COUNTIF($F$4:F17,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F17,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F17,U$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V18" s="74" t="str">
         <x:f>IF($A18="","",IF($J18="人数希望一致",1,0))</x:f>
@@ -3070,7 +3215,7 @@
         <x:f>IF('ラウンド入力'!A19="","",IF('ラウンド入力'!E19="",'設定・説明'!$B$6,'ラウンド入力'!E19))</x:f>
       </x:c>
       <x:c r="F19" s="77" t="str">
-        <x:f>IF($A19="","",IF(MAX(L19:U19)&lt;0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L19:U19),L19:U19,0))))</x:f>
+        <x:f>IF($A19="","",IF(COUNTIF(L19:U19,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L19:U19),L19:U19,0))))</x:f>
       </x:c>
       <x:c r="G19" s="77" t="str">
         <x:f>IF(OR($F19="",$F19="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F19,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -3082,40 +3227,40 @@
         <x:f>IF($A19="","",$H19+'設定・説明'!$B$7/1440)</x:f>
       </x:c>
       <x:c r="J19" s="86" t="str">
-        <x:f>IF($A19="","",IF($F19="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F19,'キャディ条件'!$A$5:$A$14,0))=$C19,"人数希望一致",IF(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F19,'キャディ条件'!$A$5:$A$14,0))="はい","2ラウンド希望を考慮","公平性・残容量"))))</x:f>
+        <x:f>IF($A19="","",IF($F19="未割当","Hard条件を満たす候補なし",IF(INDEX('キャディ条件'!$H$5:$H$14,MATCH($F19,'キャディ条件'!$A$5:$A$14,0))=$C19,"人数希望一致",IF(AND(INDEX('キャディ条件'!$F$5:$F$14,MATCH($F19,'キャディ条件'!$A$5:$A$14,0))="はい",COUNTIF($F$5:$F$19,$F19)=2),"2ラウンド希望を考慮","公平性・残容量"))))</x:f>
       </x:c>
       <x:c r="K19" s="86" t="str">
         <x:f>IF($A19="","",IF($F19="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L19" s="84" t="str">
-        <x:f>IF(OR(L$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D19),COUNTIF($F$4:F18,L$3)&lt;'キャディ条件'!$D$5,COUNTIFS($F$4:F18,L$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$5=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$5="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$5*'設定・説明'!$B$11-'キャディ条件'!$L$5*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D19),COUNTIF($F$4:F18,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F18,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F18,L$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$5=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F18,L$3)=1,AND(COUNTIF($F$4:F18,L$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F18,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F18,L$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="M19" s="84" t="str">
-        <x:f>IF(OR(M$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D19),COUNTIF($F$4:F18,M$3)&lt;'キャディ条件'!$D$6,COUNTIFS($F$4:F18,M$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$6=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$6="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$6*'設定・説明'!$B$11-'キャディ条件'!$L$6*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D19),COUNTIF($F$4:F18,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F18,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F18,M$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$6=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F18,M$3)=1,AND(COUNTIF($F$4:F18,M$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F18,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F18,M$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="N19" s="84" t="str">
-        <x:f>IF(OR(N$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D19),COUNTIF($F$4:F18,N$3)&lt;'キャディ条件'!$D$7,COUNTIFS($F$4:F18,N$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$7=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$7="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$7*'設定・説明'!$B$11-'キャディ条件'!$L$7*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D19),COUNTIF($F$4:F18,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F18,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F18,N$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$7=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F18,N$3)=1,AND(COUNTIF($F$4:F18,N$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F18,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F18,N$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="O19" s="84" t="str">
-        <x:f>IF(OR(O$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D19),COUNTIF($F$4:F18,O$3)&lt;'キャディ条件'!$D$8,COUNTIFS($F$4:F18,O$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$8=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$8="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$8*'設定・説明'!$B$11-'キャディ条件'!$L$8*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D19),COUNTIF($F$4:F18,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F18,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F18,O$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$8=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F18,O$3)=1,AND(COUNTIF($F$4:F18,O$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F18,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F18,O$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="P19" s="84" t="str">
-        <x:f>IF(OR(P$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D19),COUNTIF($F$4:F18,P$3)&lt;'キャディ条件'!$D$9,COUNTIFS($F$4:F18,P$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$9=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$9="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$9*'設定・説明'!$B$11-'キャディ条件'!$L$9*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D19),COUNTIF($F$4:F18,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F18,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F18,P$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$9=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F18,P$3)=1,AND(COUNTIF($F$4:F18,P$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F18,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F18,P$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="Q19" s="84" t="str">
-        <x:f>IF(OR(Q$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D19),COUNTIF($F$4:F18,Q$3)&lt;'キャディ条件'!$D$10,COUNTIFS($F$4:F18,Q$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$10=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$10="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$10*'設定・説明'!$B$11-'キャディ条件'!$L$10*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D19),COUNTIF($F$4:F18,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F18,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F18,Q$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$10=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F18,Q$3)=1,AND(COUNTIF($F$4:F18,Q$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F18,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F18,Q$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="R19" s="84" t="str">
-        <x:f>IF(OR(R$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D19),COUNTIF($F$4:F18,R$3)&lt;'キャディ条件'!$D$11,COUNTIFS($F$4:F18,R$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$11=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$11="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$11*'設定・説明'!$B$11-'キャディ条件'!$L$11*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D19),COUNTIF($F$4:F18,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F18,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F18,R$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$11=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F18,R$3)=1,AND(COUNTIF($F$4:F18,R$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F18,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F18,R$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="S19" s="84" t="str">
-        <x:f>IF(OR(S$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D19),COUNTIF($F$4:F18,S$3)&lt;'キャディ条件'!$D$12,COUNTIFS($F$4:F18,S$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$12=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$12="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$12*'設定・説明'!$B$11-'キャディ条件'!$L$12*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D19),COUNTIF($F$4:F18,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F18,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F18,S$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$12=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F18,S$3)=1,AND(COUNTIF($F$4:F18,S$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F18,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F18,S$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="T19" s="84" t="str">
-        <x:f>IF(OR(T$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D19),COUNTIF($F$4:F18,T$3)&lt;'キャディ条件'!$D$13,COUNTIFS($F$4:F18,T$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$13=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$13="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$13*'設定・説明'!$B$11-'キャディ条件'!$L$13*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D19),COUNTIF($F$4:F18,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F18,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F18,T$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$13=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F18,T$3)=1,AND(COUNTIF($F$4:F18,T$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F18,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F18,T$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="U19" s="84" t="str">
-        <x:f>IF(OR(U$3="",$A19=""),"",IF(AND(OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D19),COUNTIF($F$4:F18,U$3)&lt;'キャディ条件'!$D$14,COUNTIFS($F$4:F18,U$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$14=$C19,'設定・説明'!$B$9,0)+IF('キャディ条件'!$F$14="はい",'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C19=4),'設定・説明'!$B$13,0)-'キャディ条件'!$K$14*'設定・説明'!$B$11-'キャディ条件'!$L$14*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D19),COUNTIF($F$4:F18,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F18,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F18,U$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$14=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F18,U$3)=1,AND(COUNTIF($F$4:F18,U$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F18,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F18,U$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
       </x:c>
       <x:c r="V19" s="77" t="str">
         <x:f>IF($A19="","",IF($J19="人数希望一致",1,0))</x:f>
@@ -3138,6 +3283,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R063d9e65e2454623"/>
 </x:worksheet>
 </file>
 
@@ -3761,7 +3907,7 @@
         <x:v>本日の上限到達</x:v>
       </x:c>
       <x:c r="H8" s="102" t="str">
-        <x:v>Fieldスタッフprofile／汎用配置上限</x:v>
+        <x:v>CourseBoardローカルのゴルフ固有の日次ラウンド上限</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="56" customHeight="1">
@@ -3787,7 +3933,7 @@
         <x:v>2ラウンド希望を考慮</x:v>
       </x:c>
       <x:c r="H9" s="102" t="str">
-        <x:v>既存の日別availabilityの2ラウンド希望</x:v>
+        <x:v>CourseBoardローカルの当日ラウンド希望。勤務時間窓はFieldの汎用availabilityを参照</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="56" customHeight="1">

--- a/docs/src/business/caddie-assignment-simulation.xlsx
+++ b/docs/src/business/caddie-assignment-simulation.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定・説明" sheetId="1" r:id="Rcf11fd7e8b0b47b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キャディ条件" sheetId="2" r:id="Re52a65fec4914587"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラウンド入力" sheetId="3" r:id="R89f6e98413214c12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="割当シミュレーション" sheetId="4" r:id="R0b0e36ea280740a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人集計" sheetId="5" r:id="R1f8721b9b67849c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シチュエーション例" sheetId="6" r:id="Rd66f3fcf7f67403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="設定・説明" sheetId="1" r:id="R8f32309c5eed434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キャディ条件" sheetId="2" r:id="Rf3176f0cc2cc4b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラウンド入力" sheetId="3" r:id="Rdc851ba9d8a04bb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="割当シミュレーション" sheetId="4" r:id="R35cf78d591b146c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個人集計" sheetId="5" r:id="R8f866c4aefa44ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シチュエーション例" sheetId="6" r:id="R16174b3ad05d4eea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -75,7 +75,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="22">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -122,8 +122,68 @@
         <x:fgColor rgb="FFEEF5F1"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234E3A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F1EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3E7251"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F2FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234E3A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F1EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3E7251"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F2FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234E3A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F1EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3E7251"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F2FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="17">
+  <x:borders count="20">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -277,11 +337,29 @@
         <x:color rgb="FFC8D7CE"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFCAD5CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFCAD5CE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFCAD5CE"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFCAD5CE"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="118">
+  <x:cellXfs count="204">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -506,11 +584,147 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="17" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="15" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="20" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="21" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="21" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="20" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="0" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="10">
+  <x:dxfs count="13">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -612,8 +826,38 @@
         <x:color rgb="FFB42318"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFDE2E1"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA61B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA61B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE8E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA61B1B"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFDE2E1"/>
+          <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -1015,7 +1259,7 @@
         <x:v>Hard条件</x:v>
       </x:c>
       <x:c r="C16" s="31" t="str">
-        <x:v>勤務区分、ID一意性、2R可、最大組人数、担当可能コース、最大ラウンド数、時間重複を満たさない候補は -9999 点。</x:v>
+        <x:v>勤務区分、対象日勤務可否、勤務開始・終了、最大組人数、担当可能コース、最大ラウンド数、時間重複をHard適合フラグで判定する。</x:v>
       </x:c>
       <x:c r="D16" s="31"/>
       <x:c r="E16" s="31"/>
@@ -1063,7 +1307,7 @@
         <x:v>公平性</x:v>
       </x:c>
       <x:c r="C19" s="34" t="str">
-        <x:v>既存実績に加え、先行行で確定した今回割当も累積して公平性を再計算する。重みは上の設定で変更可能。</x:v>
+        <x:v>既存実績と、このシミュレーション内で先に割り当てた担当数・4人組数を合算して減点する。点数が負でもHard適合なら候補に残す。</x:v>
       </x:c>
       <x:c r="D19" s="34"/>
       <x:c r="E19" s="34"/>
@@ -1186,43 +1430,54 @@
     <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="188" t="str">
         <x:v>キャディ条件（架空データ）</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-      <x:c r="I1" s="3"/>
-      <x:c r="J1" s="3"/>
-      <x:c r="K1" s="3"/>
-      <x:c r="L1" s="3"/>
-      <x:c r="M1" s="3"/>
-      <x:c r="N1" s="3"/>
+      <x:c r="B1" s="188"/>
+      <x:c r="C1" s="188"/>
+      <x:c r="D1" s="188"/>
+      <x:c r="E1" s="188"/>
+      <x:c r="F1" s="188"/>
+      <x:c r="G1" s="188"/>
+      <x:c r="H1" s="188"/>
+      <x:c r="I1" s="188"/>
+      <x:c r="J1" s="188"/>
+      <x:c r="K1" s="188"/>
+      <x:c r="L1" s="188"/>
+      <x:c r="M1" s="188"/>
+      <x:c r="N1" s="188"/>
+      <x:c r="O1" s="189"/>
+      <x:c r="P1" s="189"/>
+      <x:c r="Q1" s="189"/>
+      <x:c r="R1" s="189"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="4" t="str">
-        <x:v>青いセルを編集してください。Hard条件と希望を分けて入力します。ID重複は割当を停止します。</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
-      <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
-      <x:c r="H2" s="4"/>
-      <x:c r="I2" s="4"/>
-      <x:c r="J2" s="4"/>
-      <x:c r="K2" s="4"/>
-      <x:c r="L2" s="4"/>
-      <x:c r="M2" s="4"/>
-      <x:c r="N2" s="4"/>
+      <x:c r="A2" s="190" t="str">
+        <x:v>青いセルを編集してください。曜日条件に加え、対象日勤務可否と勤務開始・終了を Hard 条件として判定します。</x:v>
+      </x:c>
+      <x:c r="B2" s="190"/>
+      <x:c r="C2" s="190"/>
+      <x:c r="D2" s="190"/>
+      <x:c r="E2" s="190"/>
+      <x:c r="F2" s="190"/>
+      <x:c r="G2" s="190"/>
+      <x:c r="H2" s="190"/>
+      <x:c r="I2" s="190"/>
+      <x:c r="J2" s="190"/>
+      <x:c r="K2" s="190"/>
+      <x:c r="L2" s="190"/>
+      <x:c r="M2" s="190"/>
+      <x:c r="N2" s="190"/>
+      <x:c r="O2" s="190"/>
+      <x:c r="P2" s="190"/>
+      <x:c r="Q2" s="190"/>
+      <x:c r="R2" s="190"/>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="59" t="str">
@@ -1270,6 +1525,15 @@
       <x:c r="O4" s="115" t="str">
         <x:v>ID検証</x:v>
       </x:c>
+      <x:c r="P4" s="191" t="str">
+        <x:v>対象日勤務可</x:v>
+      </x:c>
+      <x:c r="Q4" s="192" t="str">
+        <x:v>勤務開始</x:v>
+      </x:c>
+      <x:c r="R4" s="192" t="str">
+        <x:v>勤務終了</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="61" t="str">
@@ -1318,6 +1582,15 @@
         <x:f>IF(A5="","",IF(COUNTIF($A$5:$A$14,A5)&gt;1,"重複ID（割当停止）","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="P5" s="193" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q5" s="194" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R5" s="194" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="61" t="str">
@@ -1366,6 +1639,15 @@
         <x:f>IF(A6="","",IF(COUNTIF($A$5:$A$14,A6)&gt;1,"重複ID（割当停止）","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="P6" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q6" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R6" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="61" t="str">
@@ -1412,6 +1694,15 @@
         <x:f>IF(A7="","",IF(COUNTIF($A$5:$A$14,A7)&gt;1,"重複ID（割当停止）","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="P7" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q7" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R7" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="61" t="str">
@@ -1458,6 +1749,15 @@
         <x:f>IF(A8="","",IF(COUNTIF($A$5:$A$14,A8)&gt;1,"重複ID（割当停止）","OK"))</x:f>
         <x:v>OK</x:v>
       </x:c>
+      <x:c r="P8" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q8" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R8" s="196" t="n">
+        <x:v>0.625</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="61" t="str">
@@ -1503,6 +1803,15 @@
       <x:c r="O9" s="117" t="str">
         <x:f>IF(A9="","",IF(COUNTIF($A$5:$A$14,A9)&gt;1,"重複ID（割当停止）","OK"))</x:f>
         <x:v>OK</x:v>
+      </x:c>
+      <x:c r="P9" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q9" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R9" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1543,6 +1852,15 @@
       <x:c r="O10" s="117" t="str">
         <x:f>IF(A10="","",IF(COUNTIF($A$5:$A$14,A10)&gt;1,"重複ID（割当停止）","OK"))</x:f>
       </x:c>
+      <x:c r="P10" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q10" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R10" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="61"/>
@@ -1582,6 +1900,15 @@
       <x:c r="O11" s="117" t="str">
         <x:f>IF(A11="","",IF(COUNTIF($A$5:$A$14,A11)&gt;1,"重複ID（割当停止）","OK"))</x:f>
       </x:c>
+      <x:c r="P11" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q11" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R11" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="61"/>
@@ -1621,6 +1948,15 @@
       <x:c r="O12" s="117" t="str">
         <x:f>IF(A12="","",IF(COUNTIF($A$5:$A$14,A12)&gt;1,"重複ID（割当停止）","OK"))</x:f>
       </x:c>
+      <x:c r="P12" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q12" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R12" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="61"/>
@@ -1660,6 +1996,15 @@
       <x:c r="O13" s="117" t="str">
         <x:f>IF(A13="","",IF(COUNTIF($A$5:$A$14,A13)&gt;1,"重複ID（割当停止）","OK"))</x:f>
       </x:c>
+      <x:c r="P13" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q13" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R13" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="63"/>
@@ -1699,16 +2044,25 @@
       <x:c r="O14" s="117" t="str">
         <x:f>IF(A14="","",IF(COUNTIF($A$5:$A$14,A14)&gt;1,"重複ID（割当停止）","OK"))</x:f>
       </x:c>
+      <x:c r="P14" s="195" t="str">
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="Q14" s="196" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="R14" s="196" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:O1"/>
-    <x:mergeCell ref="A2:O2"/>
+    <x:mergeCell ref="A1:R1"/>
+    <x:mergeCell ref="A2:R2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="O5:O14">
     <x:cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="重複ID"/>
   </x:conditionalFormatting>
-  <x:dataValidations count="6">
+  <x:dataValidations count="7">
     <x:dataValidation type="list" sqref="C5:C14">
       <x:formula1>"全日,土日,平日"</x:formula1>
     </x:dataValidation>
@@ -1729,6 +2083,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>4</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="P5:P14">
+      <x:formula1>"はい,いいえ"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1743,25 +2100,28 @@
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="188" t="str">
         <x:v>ラウンド入力（対象日連動）</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
+      <x:c r="B1" s="188"/>
+      <x:c r="C1" s="188"/>
+      <x:c r="D1" s="188"/>
+      <x:c r="E1" s="188"/>
+      <x:c r="F1" s="189"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="4" t="str">
-        <x:v>開始時刻の順で入力してください。日付は設定シートの対象日に連動し、所要時間が空欄なら既定値を使います。</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
+      <x:c r="A2" s="190" t="str">
+        <x:v>開始時刻の昇順で入力してください。F列の時刻を編集すると、B列は設定シートの対象日へ自動連動します。</x:v>
+      </x:c>
+      <x:c r="B2" s="190"/>
+      <x:c r="C2" s="190"/>
+      <x:c r="D2" s="190"/>
+      <x:c r="E2" s="190"/>
+      <x:c r="F2" s="190"/>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="59" t="str">
@@ -1779,13 +2139,16 @@
       <x:c r="E4" s="60" t="str">
         <x:v>所要時間（分）</x:v>
       </x:c>
+      <x:c r="F4" s="197" t="str">
+        <x:v>開始時刻（入力）</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="61" t="str">
         <x:v>R1</x:v>
       </x:c>
       <x:c r="B5" s="71" t="n">
-        <x:f>IF(A5="","",'設定・説明'!$B$5+TIME(7,0,0))</x:f>
+        <x:f>IF(A5="","",'設定・説明'!$B$5+F5)</x:f>
         <x:v>46270.291666666664</x:v>
       </x:c>
       <x:c r="C5" s="62" t="n">
@@ -1796,6 +2159,9 @@
       </x:c>
       <x:c r="E5" s="62" t="n">
         <x:v>270</x:v>
+      </x:c>
+      <x:c r="F5" s="198" t="n">
+        <x:v>0.2916666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1803,7 +2169,7 @@
         <x:v>R2</x:v>
       </x:c>
       <x:c r="B6" s="71" t="n">
-        <x:f>IF(A6="","",'設定・説明'!$B$5+TIME(7,20,0))</x:f>
+        <x:f>IF(A6="","",'設定・説明'!$B$5+F6)</x:f>
         <x:v>46270.305555555555</x:v>
       </x:c>
       <x:c r="C6" s="62" t="n">
@@ -1814,6 +2180,9 @@
       </x:c>
       <x:c r="E6" s="62" t="n">
         <x:v>270</x:v>
+      </x:c>
+      <x:c r="F6" s="199" t="n">
+        <x:v>0.3055555555555556</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1821,7 +2190,7 @@
         <x:v>R3</x:v>
       </x:c>
       <x:c r="B7" s="71" t="n">
-        <x:f>IF(A7="","",'設定・説明'!$B$5+TIME(8,0,0))</x:f>
+        <x:f>IF(A7="","",'設定・説明'!$B$5+F7)</x:f>
         <x:v>46270.333333333336</x:v>
       </x:c>
       <x:c r="C7" s="62" t="n">
@@ -1832,6 +2201,9 @@
       </x:c>
       <x:c r="E7" s="62" t="n">
         <x:v>270</x:v>
+      </x:c>
+      <x:c r="F7" s="199" t="n">
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1839,7 +2211,7 @@
         <x:v>R4</x:v>
       </x:c>
       <x:c r="B8" s="71" t="n">
-        <x:f>IF(A8="","",'設定・説明'!$B$5+TIME(13,30,0))</x:f>
+        <x:f>IF(A8="","",'設定・説明'!$B$5+F8)</x:f>
         <x:v>46270.5625</x:v>
       </x:c>
       <x:c r="C8" s="62" t="n">
@@ -1850,6 +2222,9 @@
       </x:c>
       <x:c r="E8" s="62" t="n">
         <x:v>270</x:v>
+      </x:c>
+      <x:c r="F8" s="199" t="n">
+        <x:v>0.5625</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1857,7 +2232,7 @@
         <x:v>R5</x:v>
       </x:c>
       <x:c r="B9" s="71" t="n">
-        <x:f>IF(A9="","",'設定・説明'!$B$5+TIME(14,0,0))</x:f>
+        <x:f>IF(A9="","",'設定・説明'!$B$5+F9)</x:f>
         <x:v>46270.583333333336</x:v>
       </x:c>
       <x:c r="C9" s="62" t="n">
@@ -1869,101 +2244,154 @@
       <x:c r="E9" s="62" t="n">
         <x:v>270</x:v>
       </x:c>
+      <x:c r="F9" s="199" t="n">
+        <x:v>0.5833333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="61"/>
-      <x:c r="B10" s="71"/>
+      <x:c r="B10" s="71" t="str">
+        <x:f>IF(A10="","",'設定・説明'!$B$5+F10)</x:f>
+      </x:c>
       <x:c r="C10" s="62"/>
       <x:c r="D10" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E10" s="62"/>
+      <x:c r="F10" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="61"/>
-      <x:c r="B11" s="71"/>
+      <x:c r="B11" s="71" t="str">
+        <x:f>IF(A11="","",'設定・説明'!$B$5+F11)</x:f>
+      </x:c>
       <x:c r="C11" s="62"/>
       <x:c r="D11" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E11" s="62"/>
+      <x:c r="F11" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="61"/>
-      <x:c r="B12" s="71"/>
+      <x:c r="B12" s="71" t="str">
+        <x:f>IF(A12="","",'設定・説明'!$B$5+F12)</x:f>
+      </x:c>
       <x:c r="C12" s="62"/>
       <x:c r="D12" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E12" s="62"/>
+      <x:c r="F12" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="61"/>
-      <x:c r="B13" s="71"/>
+      <x:c r="B13" s="71" t="str">
+        <x:f>IF(A13="","",'設定・説明'!$B$5+F13)</x:f>
+      </x:c>
       <x:c r="C13" s="62"/>
       <x:c r="D13" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E13" s="62"/>
+      <x:c r="F13" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="61"/>
-      <x:c r="B14" s="71"/>
+      <x:c r="B14" s="71" t="str">
+        <x:f>IF(A14="","",'設定・説明'!$B$5+F14)</x:f>
+      </x:c>
       <x:c r="C14" s="62"/>
       <x:c r="D14" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E14" s="62"/>
+      <x:c r="F14" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="61"/>
-      <x:c r="B15" s="71"/>
+      <x:c r="B15" s="71" t="str">
+        <x:f>IF(A15="","",'設定・説明'!$B$5+F15)</x:f>
+      </x:c>
       <x:c r="C15" s="62"/>
       <x:c r="D15" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E15" s="62"/>
+      <x:c r="F15" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="61"/>
-      <x:c r="B16" s="71"/>
+      <x:c r="B16" s="71" t="str">
+        <x:f>IF(A16="","",'設定・説明'!$B$5+F16)</x:f>
+      </x:c>
       <x:c r="C16" s="62"/>
       <x:c r="D16" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E16" s="62"/>
+      <x:c r="F16" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="61"/>
-      <x:c r="B17" s="71"/>
+      <x:c r="B17" s="71" t="str">
+        <x:f>IF(A17="","",'設定・説明'!$B$5+F17)</x:f>
+      </x:c>
       <x:c r="C17" s="62"/>
       <x:c r="D17" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E17" s="62"/>
+      <x:c r="F17" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="61"/>
-      <x:c r="B18" s="71"/>
+      <x:c r="B18" s="71" t="str">
+        <x:f>IF(A18="","",'設定・説明'!$B$5+F18)</x:f>
+      </x:c>
       <x:c r="C18" s="62"/>
       <x:c r="D18" s="62" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E18" s="62"/>
+      <x:c r="F18" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="63"/>
-      <x:c r="B19" s="72"/>
+      <x:c r="B19" s="72" t="str">
+        <x:f>IF(A19="","",'設定・説明'!$B$5+F19)</x:f>
+      </x:c>
       <x:c r="C19" s="64"/>
       <x:c r="D19" s="64" t="str">
         <x:v>OUT</x:v>
       </x:c>
       <x:c r="E19" s="64"/>
+      <x:c r="F19" s="199" t="n">
+        <x:v>0.2916666666666667</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:dataValidations count="3">
     <x:dataValidation type="whole" operator="between" sqref="C5:C19">
@@ -2008,58 +2436,89 @@
     <x:col min="20" max="20" width="11" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="11" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="12" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="10" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="10" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="10" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="10" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="10" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="10" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="10" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="10" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="10" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="3" t="str">
+      <x:c r="A1" s="188" t="str">
         <x:v>割当シミュレーション（逐次ヒューリスティック）</x:v>
       </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-      <x:c r="I1" s="3"/>
-      <x:c r="J1" s="3"/>
-      <x:c r="K1" s="3"/>
-      <x:c r="L1" s="3"/>
-      <x:c r="M1" s="3"/>
-      <x:c r="N1" s="3"/>
-      <x:c r="O1" s="3"/>
-      <x:c r="P1" s="3"/>
-      <x:c r="Q1" s="3"/>
-      <x:c r="R1" s="3"/>
-      <x:c r="S1" s="3"/>
-      <x:c r="T1" s="3"/>
-      <x:c r="U1" s="3"/>
-      <x:c r="V1" s="3"/>
+      <x:c r="B1" s="188"/>
+      <x:c r="C1" s="188"/>
+      <x:c r="D1" s="188"/>
+      <x:c r="E1" s="188"/>
+      <x:c r="F1" s="188"/>
+      <x:c r="G1" s="188"/>
+      <x:c r="H1" s="188"/>
+      <x:c r="I1" s="188"/>
+      <x:c r="J1" s="188"/>
+      <x:c r="K1" s="188"/>
+      <x:c r="L1" s="188"/>
+      <x:c r="M1" s="188"/>
+      <x:c r="N1" s="188"/>
+      <x:c r="O1" s="188"/>
+      <x:c r="P1" s="188"/>
+      <x:c r="Q1" s="188"/>
+      <x:c r="R1" s="188"/>
+      <x:c r="S1" s="188"/>
+      <x:c r="T1" s="188"/>
+      <x:c r="U1" s="188"/>
+      <x:c r="V1" s="188"/>
+      <x:c r="W1" s="189"/>
+      <x:c r="X1" s="189"/>
+      <x:c r="Y1" s="189"/>
+      <x:c r="Z1" s="189"/>
+      <x:c r="AA1" s="189"/>
+      <x:c r="AB1" s="189"/>
+      <x:c r="AC1" s="189"/>
+      <x:c r="AD1" s="189"/>
+      <x:c r="AE1" s="189"/>
+      <x:c r="AF1" s="189"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="4" t="str">
-        <x:v>各候補の点数を右側に表示します。-9999はHard条件不適合です。割当は入力行の上から順に決まります。</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
-      <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
-      <x:c r="H2" s="4"/>
-      <x:c r="I2" s="4"/>
-      <x:c r="J2" s="4"/>
-      <x:c r="K2" s="4"/>
-      <x:c r="L2" s="4"/>
-      <x:c r="M2" s="4"/>
-      <x:c r="N2" s="4"/>
-      <x:c r="O2" s="4"/>
-      <x:c r="P2" s="4"/>
-      <x:c r="Q2" s="4"/>
-      <x:c r="R2" s="4"/>
-      <x:c r="S2" s="4"/>
-      <x:c r="T2" s="4"/>
-      <x:c r="U2" s="4"/>
+      <x:c r="A2" s="190" t="str">
+        <x:v>点数（L〜U）とHard適合（W〜AF）を分離しています。適合=1の候補だけを比較し、点数が負でも割当可能です。</x:v>
+      </x:c>
+      <x:c r="B2" s="190"/>
+      <x:c r="C2" s="190"/>
+      <x:c r="D2" s="190"/>
+      <x:c r="E2" s="190"/>
+      <x:c r="F2" s="190"/>
+      <x:c r="G2" s="190"/>
+      <x:c r="H2" s="190"/>
+      <x:c r="I2" s="190"/>
+      <x:c r="J2" s="190"/>
+      <x:c r="K2" s="190"/>
+      <x:c r="L2" s="190"/>
+      <x:c r="M2" s="190"/>
+      <x:c r="N2" s="190"/>
+      <x:c r="O2" s="190"/>
+      <x:c r="P2" s="190"/>
+      <x:c r="Q2" s="190"/>
+      <x:c r="R2" s="190"/>
+      <x:c r="S2" s="190"/>
+      <x:c r="T2" s="190"/>
+      <x:c r="U2" s="190"/>
+      <x:c r="V2" s="190"/>
+      <x:c r="W2" s="190"/>
+      <x:c r="X2" s="190"/>
+      <x:c r="Y2" s="190"/>
+      <x:c r="Z2" s="190"/>
+      <x:c r="AA2" s="190"/>
+      <x:c r="AB2" s="190"/>
+      <x:c r="AC2" s="190"/>
+      <x:c r="AD2" s="190"/>
+      <x:c r="AE2" s="190"/>
+      <x:c r="AF2" s="190"/>
     </x:row>
     <x:row r="3">
       <x:c r="L3" t="str">
@@ -2097,6 +2556,41 @@
       <x:c r="U3" t="str">
         <x:f>IF('キャディ条件'!A14="","",'キャディ条件'!A14)</x:f>
       </x:c>
+      <x:c r="W3" t="str">
+        <x:f>IF('キャディ条件'!A5="","",'キャディ条件'!A5)</x:f>
+        <x:v>cad_sato</x:v>
+      </x:c>
+      <x:c r="X3" t="str">
+        <x:f>IF('キャディ条件'!A6="","",'キャディ条件'!A6)</x:f>
+        <x:v>cad_suzuki</x:v>
+      </x:c>
+      <x:c r="Y3" t="str">
+        <x:f>IF('キャディ条件'!A7="","",'キャディ条件'!A7)</x:f>
+        <x:v>cad_tanaka</x:v>
+      </x:c>
+      <x:c r="Z3" t="str">
+        <x:f>IF('キャディ条件'!A8="","",'キャディ条件'!A8)</x:f>
+        <x:v>cad_yamamoto</x:v>
+      </x:c>
+      <x:c r="AA3" t="str">
+        <x:f>IF('キャディ条件'!A9="","",'キャディ条件'!A9)</x:f>
+        <x:v>cad_ito</x:v>
+      </x:c>
+      <x:c r="AB3" t="str">
+        <x:f>IF('キャディ条件'!A10="","",'キャディ条件'!A10)</x:f>
+      </x:c>
+      <x:c r="AC3" t="str">
+        <x:f>IF('キャディ条件'!A11="","",'キャディ条件'!A11)</x:f>
+      </x:c>
+      <x:c r="AD3" t="str">
+        <x:f>IF('キャディ条件'!A12="","",'キャディ条件'!A12)</x:f>
+      </x:c>
+      <x:c r="AE3" t="str">
+        <x:f>IF('キャディ条件'!A13="","",'キャディ条件'!A13)</x:f>
+      </x:c>
+      <x:c r="AF3" t="str">
+        <x:f>IF('キャディ条件'!A14="","",'キャディ条件'!A14)</x:f>
+      </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="59" t="str">
@@ -2164,6 +2658,36 @@
       </x:c>
       <x:c r="V4" s="60" t="str">
         <x:v>希望一致</x:v>
+      </x:c>
+      <x:c r="W4" s="200" t="str">
+        <x:v>候補1可</x:v>
+      </x:c>
+      <x:c r="X4" s="201" t="str">
+        <x:v>候補2可</x:v>
+      </x:c>
+      <x:c r="Y4" s="201" t="str">
+        <x:v>候補3可</x:v>
+      </x:c>
+      <x:c r="Z4" s="201" t="str">
+        <x:v>候補4可</x:v>
+      </x:c>
+      <x:c r="AA4" s="201" t="str">
+        <x:v>候補5可</x:v>
+      </x:c>
+      <x:c r="AB4" s="201" t="str">
+        <x:v>候補6可</x:v>
+      </x:c>
+      <x:c r="AC4" s="201" t="str">
+        <x:v>候補7可</x:v>
+      </x:c>
+      <x:c r="AD4" s="201" t="str">
+        <x:v>候補8可</x:v>
+      </x:c>
+      <x:c r="AE4" s="201" t="str">
+        <x:v>候補9可</x:v>
+      </x:c>
+      <x:c r="AF4" s="201" t="str">
+        <x:v>候補10可</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2188,7 +2712,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F5" s="74" t="str">
-        <x:f>IF($A5="","",IF(COUNTIF(L5:U5,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L5:U5),L5:U5,0))))</x:f>
+        <x:f>IF($A5="","",IF(SUM(W5:AF5)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L5:U5),L5:U5,0))))</x:f>
         <x:v>cad_tanaka</x:v>
       </x:c>
       <x:c r="G5" s="74" t="str">
@@ -2210,44 +2734,77 @@
       <x:c r="K5" s="85" t="str">
         <x:f>IF($A5="","",IF($F5="未割当","要手動調整",""))</x:f>
       </x:c>
-      <x:c r="L5" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D5),COUNTIF($F$4:F4,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F4,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F4,L$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$5=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F4,L$3)=1,AND(COUNTIF($F$4:F4,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F4,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F4,L$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="L5" s="83" t="str">
+        <x:f>IF(OR(L$3="",$A5=""),"",IF(W5=1,100+IF('キャディ条件'!$H$5=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F4,L$3)=1,AND(COUNTIF($F$4:F4,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F4,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F4,L$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M5" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D5),COUNTIF($F$4:F4,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F4,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F4,M$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$6=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F4,M$3)=1,AND(COUNTIF($F$4:F4,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F4,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F4,M$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A5=""),"",IF(X5=1,100+IF('キャディ条件'!$H$6=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F4,M$3)=1,AND(COUNTIF($F$4:F4,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F4,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F4,M$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>115</x:v>
       </x:c>
       <x:c r="N5" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D5),COUNTIF($F$4:F4,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F4,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F4,N$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$7=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F4,N$3)=1,AND(COUNTIF($F$4:F4,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F4,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F4,N$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A5=""),"",IF(Y5=1,100+IF('キャディ条件'!$H$7=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F4,N$3)=1,AND(COUNTIF($F$4:F4,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F4,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F4,N$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>127</x:v>
       </x:c>
-      <x:c r="O5" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D5),COUNTIF($F$4:F4,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F4,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F4,O$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$8=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F4,O$3)=1,AND(COUNTIF($F$4:F4,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F4,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F4,O$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="O5" s="83" t="str">
+        <x:f>IF(OR(O$3="",$A5=""),"",IF(Z5=1,100+IF('キャディ条件'!$H$8=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F4,O$3)=1,AND(COUNTIF($F$4:F4,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F4,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F4,O$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P5" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D5),COUNTIF($F$4:F4,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F4,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F4,P$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$9=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F4,P$3)=1,AND(COUNTIF($F$4:F4,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F4,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F4,P$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A5=""),"",IF(AA5=1,100+IF('キャディ条件'!$H$9=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F4,P$3)=1,AND(COUNTIF($F$4:F4,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F4,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F4,P$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q5" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D5),COUNTIF($F$4:F4,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F4,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F4,Q$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$10=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F4,Q$3)=1,AND(COUNTIF($F$4:F4,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F4,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F4,Q$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A5=""),"",IF(AB5=1,100+IF('キャディ条件'!$H$10=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F4,Q$3)=1,AND(COUNTIF($F$4:F4,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F4,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F4,Q$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R5" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D5),COUNTIF($F$4:F4,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F4,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F4,R$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$11=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F4,R$3)=1,AND(COUNTIF($F$4:F4,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F4,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F4,R$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A5=""),"",IF(AC5=1,100+IF('キャディ条件'!$H$11=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F4,R$3)=1,AND(COUNTIF($F$4:F4,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F4,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F4,R$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S5" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D5),COUNTIF($F$4:F4,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F4,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F4,S$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$12=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F4,S$3)=1,AND(COUNTIF($F$4:F4,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F4,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F4,S$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A5=""),"",IF(AD5=1,100+IF('キャディ条件'!$H$12=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F4,S$3)=1,AND(COUNTIF($F$4:F4,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F4,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F4,S$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T5" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D5),COUNTIF($F$4:F4,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F4,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F4,T$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$13=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F4,T$3)=1,AND(COUNTIF($F$4:F4,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F4,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F4,T$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A5=""),"",IF(AE5=1,100+IF('キャディ条件'!$H$13=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F4,T$3)=1,AND(COUNTIF($F$4:F4,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F4,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F4,T$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U5" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B5,2)&lt;=5)),$C5&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D5),COUNTIF($F$4:F4,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F4,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F4,U$3,$I$4:I4,"&gt;"&amp;$B5)=0),100+IF('キャディ条件'!$H$14=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F4,U$3)=1,AND(COUNTIF($F$4:F4,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F4,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F4,U$3,$C$4:C4,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A5=""),"",IF(AF5=1,100+IF('キャディ条件'!$H$14=$C5,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F4,U$3)=1,AND(COUNTIF($F$4:F4,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$6:$A$19,"&lt;&gt;",'ラウンド入力'!$B$6:$B$19,"&gt;="&amp;($B5+$E5/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$6:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$6:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C5=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F4,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F4,U$3,$C$4:C4,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V5" s="74" t="n">
         <x:f>IF($A5="","",IF($J5="人数希望一致",1,0))</x:f>
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="W5" s="202" t="n">
+        <x:f>IF(OR(L$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$5,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C5&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D5),COUNTIF($F$4:F4,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F4,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F4,L$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X5" s="203" t="n">
+        <x:f>IF(OR(M$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$6,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C5&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D5),COUNTIF($F$4:F4,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F4,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F4,M$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y5" s="203" t="n">
+        <x:f>IF(OR(N$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$7,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C5&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D5),COUNTIF($F$4:F4,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F4,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F4,N$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z5" s="203" t="n">
+        <x:f>IF(OR(O$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$8,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C5&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D5),COUNTIF($F$4:F4,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F4,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F4,O$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA5" s="203" t="n">
+        <x:f>IF(OR(P$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$9,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C5&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D5),COUNTIF($F$4:F4,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F4,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F4,P$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB5" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$10,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C5&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D5),COUNTIF($F$4:F4,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F4,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F4,Q$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC5" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$11,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C5&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D5),COUNTIF($F$4:F4,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F4,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F4,R$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD5" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$12,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C5&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D5),COUNTIF($F$4:F4,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F4,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F4,S$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE5" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$13,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C5&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D5),COUNTIF($F$4:F4,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F4,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F4,T$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF5" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A5=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B5,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B5,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B5,1)&gt;='キャディ条件'!$Q$14,MOD($B5+$E5/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C5&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D5),COUNTIF($F$4:F4,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F4,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F4,U$3,$I$4:I4,"&gt;"&amp;$B5)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2272,7 +2829,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F6" s="74" t="str">
-        <x:f>IF($A6="","",IF(COUNTIF(L6:U6,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L6:U6),L6:U6,0))))</x:f>
+        <x:f>IF($A6="","",IF(SUM(W6:AF6)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L6:U6),L6:U6,0))))</x:f>
         <x:v>cad_sato</x:v>
       </x:c>
       <x:c r="G6" s="74" t="str">
@@ -2295,43 +2852,76 @@
         <x:f>IF($A6="","",IF($F6="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L6" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D6),COUNTIF($F$4:F5,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F5,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F5,L$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$5=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F5,L$3)=1,AND(COUNTIF($F$4:F5,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F5,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F5,L$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A6=""),"",IF(W6=1,100+IF('キャディ条件'!$H$5=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F5,L$3)=1,AND(COUNTIF($F$4:F5,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F5,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F5,L$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>122</x:v>
       </x:c>
       <x:c r="M6" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D6),COUNTIF($F$4:F5,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F5,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F5,M$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$6=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F5,M$3)=1,AND(COUNTIF($F$4:F5,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F5,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F5,M$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A6=""),"",IF(X6=1,100+IF('キャディ条件'!$H$6=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F5,M$3)=1,AND(COUNTIF($F$4:F5,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F5,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F5,M$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>75</x:v>
       </x:c>
-      <x:c r="N6" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D6),COUNTIF($F$4:F5,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F5,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F5,N$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$7=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F5,N$3)=1,AND(COUNTIF($F$4:F5,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F5,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F5,N$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
-      </x:c>
-      <x:c r="O6" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D6),COUNTIF($F$4:F5,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F5,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F5,O$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$8=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F5,O$3)=1,AND(COUNTIF($F$4:F5,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F5,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F5,O$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="N6" s="83" t="str">
+        <x:f>IF(OR(N$3="",$A6=""),"",IF(Y6=1,100+IF('キャディ条件'!$H$7=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F5,N$3)=1,AND(COUNTIF($F$4:F5,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F5,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F5,N$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
+      </x:c>
+      <x:c r="O6" s="83" t="str">
+        <x:f>IF(OR(O$3="",$A6=""),"",IF(Z6=1,100+IF('キャディ条件'!$H$8=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F5,O$3)=1,AND(COUNTIF($F$4:F5,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F5,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F5,O$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P6" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D6),COUNTIF($F$4:F5,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F5,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F5,P$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$9=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F5,P$3)=1,AND(COUNTIF($F$4:F5,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F5,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F5,P$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A6=""),"",IF(AA6=1,100+IF('キャディ条件'!$H$9=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F5,P$3)=1,AND(COUNTIF($F$4:F5,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F5,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F5,P$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q6" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D6),COUNTIF($F$4:F5,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F5,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F5,Q$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$10=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F5,Q$3)=1,AND(COUNTIF($F$4:F5,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F5,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F5,Q$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A6=""),"",IF(AB6=1,100+IF('キャディ条件'!$H$10=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F5,Q$3)=1,AND(COUNTIF($F$4:F5,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F5,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F5,Q$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R6" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D6),COUNTIF($F$4:F5,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F5,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F5,R$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$11=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F5,R$3)=1,AND(COUNTIF($F$4:F5,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F5,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F5,R$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A6=""),"",IF(AC6=1,100+IF('キャディ条件'!$H$11=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F5,R$3)=1,AND(COUNTIF($F$4:F5,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F5,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F5,R$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S6" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D6),COUNTIF($F$4:F5,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F5,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F5,S$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$12=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F5,S$3)=1,AND(COUNTIF($F$4:F5,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F5,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F5,S$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A6=""),"",IF(AD6=1,100+IF('キャディ条件'!$H$12=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F5,S$3)=1,AND(COUNTIF($F$4:F5,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F5,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F5,S$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T6" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D6),COUNTIF($F$4:F5,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F5,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F5,T$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$13=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F5,T$3)=1,AND(COUNTIF($F$4:F5,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F5,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F5,T$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A6=""),"",IF(AE6=1,100+IF('キャディ条件'!$H$13=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F5,T$3)=1,AND(COUNTIF($F$4:F5,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F5,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F5,T$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U6" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B6,2)&lt;=5)),$C6&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D6),COUNTIF($F$4:F5,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F5,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F5,U$3,$I$4:I5,"&gt;"&amp;$B6)=0),100+IF('キャディ条件'!$H$14=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F5,U$3)=1,AND(COUNTIF($F$4:F5,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F5,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F5,U$3,$C$4:C5,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A6=""),"",IF(AF6=1,100+IF('キャディ条件'!$H$14=$C6,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F5,U$3)=1,AND(COUNTIF($F$4:F5,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$7:$A$19,"&lt;&gt;",'ラウンド入力'!$B$7:$B$19,"&gt;="&amp;($B6+$E6/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$7:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$7:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C6=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F5,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F5,U$3,$C$4:C5,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V6" s="74" t="n">
         <x:f>IF($A6="","",IF($J6="人数希望一致",1,0))</x:f>
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="W6" s="202" t="n">
+        <x:f>IF(OR(L$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$5,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C6&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D6),COUNTIF($F$4:F5,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F5,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F5,L$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X6" s="203" t="n">
+        <x:f>IF(OR(M$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$6,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C6&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D6),COUNTIF($F$4:F5,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F5,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F5,M$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y6" s="203" t="n">
+        <x:f>IF(OR(N$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$7,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C6&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D6),COUNTIF($F$4:F5,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F5,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F5,N$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z6" s="203" t="n">
+        <x:f>IF(OR(O$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$8,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C6&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D6),COUNTIF($F$4:F5,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F5,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F5,O$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA6" s="203" t="n">
+        <x:f>IF(OR(P$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$9,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C6&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D6),COUNTIF($F$4:F5,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F5,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F5,P$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB6" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$10,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C6&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D6),COUNTIF($F$4:F5,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F5,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F5,Q$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC6" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$11,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C6&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D6),COUNTIF($F$4:F5,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F5,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F5,R$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD6" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$12,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C6&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D6),COUNTIF($F$4:F5,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F5,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F5,S$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE6" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$13,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C6&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D6),COUNTIF($F$4:F5,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F5,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F5,T$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF6" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A6=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B6,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B6,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B6,1)&gt;='キャディ条件'!$Q$14,MOD($B6+$E6/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C6&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D6),COUNTIF($F$4:F5,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F5,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F5,U$3,$I$4:I5,"&gt;"&amp;$B6)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2356,7 +2946,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F7" s="74" t="str">
-        <x:f>IF($A7="","",IF(COUNTIF(L7:U7,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L7:U7),L7:U7,0))))</x:f>
+        <x:f>IF($A7="","",IF(SUM(W7:AF7)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L7:U7),L7:U7,0))))</x:f>
         <x:v>cad_suzuki</x:v>
       </x:c>
       <x:c r="G7" s="74" t="str">
@@ -2378,44 +2968,76 @@
       <x:c r="K7" s="85" t="str">
         <x:f>IF($A7="","",IF($F7="未割当","要手動調整",""))</x:f>
       </x:c>
-      <x:c r="L7" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D7),COUNTIF($F$4:F6,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F6,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F6,L$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$5=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F6,L$3)=1,AND(COUNTIF($F$4:F6,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F6,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F6,L$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="L7" s="83" t="str">
+        <x:f>IF(OR(L$3="",$A7=""),"",IF(W7=1,100+IF('キャディ条件'!$H$5=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F6,L$3)=1,AND(COUNTIF($F$4:F6,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F6,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F6,L$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M7" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D7),COUNTIF($F$4:F6,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F6,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F6,M$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$6=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F6,M$3)=1,AND(COUNTIF($F$4:F6,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F6,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F6,M$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A7=""),"",IF(X7=1,100+IF('キャディ条件'!$H$6=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F6,M$3)=1,AND(COUNTIF($F$4:F6,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F6,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F6,M$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>115</x:v>
       </x:c>
-      <x:c r="N7" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D7),COUNTIF($F$4:F6,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F6,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F6,N$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$7=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F6,N$3)=1,AND(COUNTIF($F$4:F6,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F6,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F6,N$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
-      </x:c>
-      <x:c r="O7" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D7),COUNTIF($F$4:F6,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F6,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F6,O$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$8=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F6,O$3)=1,AND(COUNTIF($F$4:F6,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F6,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F6,O$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="N7" s="83" t="str">
+        <x:f>IF(OR(N$3="",$A7=""),"",IF(Y7=1,100+IF('キャディ条件'!$H$7=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F6,N$3)=1,AND(COUNTIF($F$4:F6,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F6,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F6,N$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
+      </x:c>
+      <x:c r="O7" s="83" t="str">
+        <x:f>IF(OR(O$3="",$A7=""),"",IF(Z7=1,100+IF('キャディ条件'!$H$8=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F6,O$3)=1,AND(COUNTIF($F$4:F6,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F6,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F6,O$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P7" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D7),COUNTIF($F$4:F6,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F6,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F6,P$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$9=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F6,P$3)=1,AND(COUNTIF($F$4:F6,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F6,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F6,P$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A7=""),"",IF(AA7=1,100+IF('キャディ条件'!$H$9=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F6,P$3)=1,AND(COUNTIF($F$4:F6,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F6,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F6,P$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q7" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D7),COUNTIF($F$4:F6,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F6,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F6,Q$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$10=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F6,Q$3)=1,AND(COUNTIF($F$4:F6,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F6,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F6,Q$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A7=""),"",IF(AB7=1,100+IF('キャディ条件'!$H$10=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F6,Q$3)=1,AND(COUNTIF($F$4:F6,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F6,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F6,Q$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R7" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D7),COUNTIF($F$4:F6,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F6,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F6,R$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$11=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F6,R$3)=1,AND(COUNTIF($F$4:F6,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F6,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F6,R$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A7=""),"",IF(AC7=1,100+IF('キャディ条件'!$H$11=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F6,R$3)=1,AND(COUNTIF($F$4:F6,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F6,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F6,R$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S7" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D7),COUNTIF($F$4:F6,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F6,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F6,S$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$12=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F6,S$3)=1,AND(COUNTIF($F$4:F6,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F6,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F6,S$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A7=""),"",IF(AD7=1,100+IF('キャディ条件'!$H$12=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F6,S$3)=1,AND(COUNTIF($F$4:F6,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F6,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F6,S$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T7" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D7),COUNTIF($F$4:F6,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F6,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F6,T$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$13=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F6,T$3)=1,AND(COUNTIF($F$4:F6,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F6,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F6,T$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A7=""),"",IF(AE7=1,100+IF('キャディ条件'!$H$13=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F6,T$3)=1,AND(COUNTIF($F$4:F6,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F6,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F6,T$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U7" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B7,2)&lt;=5)),$C7&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D7),COUNTIF($F$4:F6,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F6,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F6,U$3,$I$4:I6,"&gt;"&amp;$B7)=0),100+IF('キャディ条件'!$H$14=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F6,U$3)=1,AND(COUNTIF($F$4:F6,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F6,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F6,U$3,$C$4:C6,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A7=""),"",IF(AF7=1,100+IF('キャディ条件'!$H$14=$C7,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F6,U$3)=1,AND(COUNTIF($F$4:F6,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$8:$A$19,"&lt;&gt;",'ラウンド入力'!$B$8:$B$19,"&gt;="&amp;($B7+$E7/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$8:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$8:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C7=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F6,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F6,U$3,$C$4:C6,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V7" s="74" t="n">
         <x:f>IF($A7="","",IF($J7="人数希望一致",1,0))</x:f>
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="W7" s="202" t="n">
+        <x:f>IF(OR(L$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$5,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C7&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D7),COUNTIF($F$4:F6,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F6,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F6,L$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X7" s="203" t="n">
+        <x:f>IF(OR(M$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$6,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C7&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D7),COUNTIF($F$4:F6,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F6,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F6,M$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y7" s="203" t="n">
+        <x:f>IF(OR(N$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$7,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C7&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D7),COUNTIF($F$4:F6,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F6,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F6,N$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z7" s="203" t="n">
+        <x:f>IF(OR(O$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$8,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C7&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D7),COUNTIF($F$4:F6,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F6,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F6,O$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA7" s="203" t="n">
+        <x:f>IF(OR(P$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$9,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C7&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D7),COUNTIF($F$4:F6,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F6,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F6,P$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB7" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$10,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C7&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D7),COUNTIF($F$4:F6,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F6,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F6,Q$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC7" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$11,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C7&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D7),COUNTIF($F$4:F6,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F6,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F6,R$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD7" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$12,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C7&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D7),COUNTIF($F$4:F6,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F6,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F6,S$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE7" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$13,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C7&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D7),COUNTIF($F$4:F6,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F6,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F6,T$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF7" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A7=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B7,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B7,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B7,1)&gt;='キャディ条件'!$Q$14,MOD($B7+$E7/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C7&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D7),COUNTIF($F$4:F6,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F6,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F6,U$3,$I$4:I6,"&gt;"&amp;$B7)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2440,7 +3062,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F8" s="74" t="str">
-        <x:f>IF($A8="","",IF(COUNTIF(L8:U8,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L8:U8),L8:U8,0))))</x:f>
+        <x:f>IF($A8="","",IF(SUM(W8:AF8)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L8:U8),L8:U8,0))))</x:f>
         <x:v>cad_tanaka</x:v>
       </x:c>
       <x:c r="G8" s="74" t="str">
@@ -2462,44 +3084,76 @@
       <x:c r="K8" s="85" t="str">
         <x:f>IF($A8="","",IF($F8="未割当","要手動調整",""))</x:f>
       </x:c>
-      <x:c r="L8" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D8),COUNTIF($F$4:F7,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F7,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F7,L$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$5=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F7,L$3)=1,AND(COUNTIF($F$4:F7,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F7,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F7,L$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
-      </x:c>
-      <x:c r="M8" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D8),COUNTIF($F$4:F7,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F7,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F7,M$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$6=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F7,M$3)=1,AND(COUNTIF($F$4:F7,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F7,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F7,M$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="L8" s="83" t="str">
+        <x:f>IF(OR(L$3="",$A8=""),"",IF(W8=1,100+IF('キャディ条件'!$H$5=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F7,L$3)=1,AND(COUNTIF($F$4:F7,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F7,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F7,L$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
+      </x:c>
+      <x:c r="M8" s="83" t="str">
+        <x:f>IF(OR(M$3="",$A8=""),"",IF(X8=1,100+IF('キャディ条件'!$H$6=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F7,M$3)=1,AND(COUNTIF($F$4:F7,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F7,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F7,M$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N8" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D8),COUNTIF($F$4:F7,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F7,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F7,N$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$7=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F7,N$3)=1,AND(COUNTIF($F$4:F7,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F7,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F7,N$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A8=""),"",IF(Y8=1,100+IF('キャディ条件'!$H$7=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F7,N$3)=1,AND(COUNTIF($F$4:F7,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F7,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F7,N$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>123</x:v>
       </x:c>
-      <x:c r="O8" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D8),COUNTIF($F$4:F7,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F7,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F7,O$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$8=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F7,O$3)=1,AND(COUNTIF($F$4:F7,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F7,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F7,O$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="O8" s="83" t="str">
+        <x:f>IF(OR(O$3="",$A8=""),"",IF(Z8=1,100+IF('キャディ条件'!$H$8=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F7,O$3)=1,AND(COUNTIF($F$4:F7,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F7,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F7,O$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P8" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D8),COUNTIF($F$4:F7,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F7,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F7,P$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$9=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F7,P$3)=1,AND(COUNTIF($F$4:F7,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F7,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F7,P$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A8=""),"",IF(AA8=1,100+IF('キャディ条件'!$H$9=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F7,P$3)=1,AND(COUNTIF($F$4:F7,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F7,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F7,P$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q8" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D8),COUNTIF($F$4:F7,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F7,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F7,Q$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$10=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F7,Q$3)=1,AND(COUNTIF($F$4:F7,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F7,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F7,Q$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A8=""),"",IF(AB8=1,100+IF('キャディ条件'!$H$10=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F7,Q$3)=1,AND(COUNTIF($F$4:F7,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F7,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F7,Q$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R8" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D8),COUNTIF($F$4:F7,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F7,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F7,R$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$11=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F7,R$3)=1,AND(COUNTIF($F$4:F7,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F7,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F7,R$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A8=""),"",IF(AC8=1,100+IF('キャディ条件'!$H$11=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F7,R$3)=1,AND(COUNTIF($F$4:F7,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F7,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F7,R$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S8" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D8),COUNTIF($F$4:F7,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F7,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F7,S$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$12=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F7,S$3)=1,AND(COUNTIF($F$4:F7,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F7,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F7,S$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A8=""),"",IF(AD8=1,100+IF('キャディ条件'!$H$12=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F7,S$3)=1,AND(COUNTIF($F$4:F7,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F7,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F7,S$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T8" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D8),COUNTIF($F$4:F7,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F7,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F7,T$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$13=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F7,T$3)=1,AND(COUNTIF($F$4:F7,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F7,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F7,T$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A8=""),"",IF(AE8=1,100+IF('キャディ条件'!$H$13=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F7,T$3)=1,AND(COUNTIF($F$4:F7,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F7,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F7,T$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U8" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B8,2)&lt;=5)),$C8&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D8),COUNTIF($F$4:F7,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F7,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F7,U$3,$I$4:I7,"&gt;"&amp;$B8)=0),100+IF('キャディ条件'!$H$14=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F7,U$3)=1,AND(COUNTIF($F$4:F7,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F7,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F7,U$3,$C$4:C7,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A8=""),"",IF(AF8=1,100+IF('キャディ条件'!$H$14=$C8,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F7,U$3)=1,AND(COUNTIF($F$4:F7,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$9:$A$19,"&lt;&gt;",'ラウンド入力'!$B$9:$B$19,"&gt;="&amp;($B8+$E8/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$9:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$9:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C8=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F7,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F7,U$3,$C$4:C7,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V8" s="74" t="n">
         <x:f>IF($A8="","",IF($J8="人数希望一致",1,0))</x:f>
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="W8" s="202" t="n">
+        <x:f>IF(OR(L$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$5,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C8&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D8),COUNTIF($F$4:F7,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F7,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F7,L$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X8" s="203" t="n">
+        <x:f>IF(OR(M$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$6,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C8&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D8),COUNTIF($F$4:F7,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F7,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F7,M$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y8" s="203" t="n">
+        <x:f>IF(OR(N$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$7,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C8&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D8),COUNTIF($F$4:F7,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F7,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F7,N$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z8" s="203" t="n">
+        <x:f>IF(OR(O$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$8,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C8&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D8),COUNTIF($F$4:F7,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F7,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F7,O$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA8" s="203" t="n">
+        <x:f>IF(OR(P$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$9,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C8&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D8),COUNTIF($F$4:F7,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F7,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F7,P$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB8" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$10,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C8&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D8),COUNTIF($F$4:F7,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F7,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F7,Q$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC8" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$11,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C8&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D8),COUNTIF($F$4:F7,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F7,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F7,R$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD8" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$12,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C8&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D8),COUNTIF($F$4:F7,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F7,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F7,S$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE8" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$13,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C8&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D8),COUNTIF($F$4:F7,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F7,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F7,T$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF8" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A8=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B8,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B8,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B8,1)&gt;='キャディ条件'!$Q$14,MOD($B8+$E8/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C8&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D8),COUNTIF($F$4:F7,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F7,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F7,U$3,$I$4:I7,"&gt;"&amp;$B8)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2524,7 +3178,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="F9" s="74" t="str">
-        <x:f>IF($A9="","",IF(COUNTIF(L9:U9,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L9:U9),L9:U9,0))))</x:f>
+        <x:f>IF($A9="","",IF(SUM(W9:AF9)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L9:U9),L9:U9,0))))</x:f>
         <x:v>cad_ito</x:v>
       </x:c>
       <x:c r="G9" s="74" t="str">
@@ -2546,45 +3200,76 @@
       <x:c r="K9" s="85" t="str">
         <x:f>IF($A9="","",IF($F9="未割当","要手動調整",""))</x:f>
       </x:c>
-      <x:c r="L9" s="83" t="n">
-        <x:f>IF(OR(L$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D9),COUNTIF($F$4:F8,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F8,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F8,L$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$5=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F8,L$3)=1,AND(COUNTIF($F$4:F8,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F8,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F8,L$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
-      </x:c>
-      <x:c r="M9" s="83" t="n">
-        <x:f>IF(OR(M$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D9),COUNTIF($F$4:F8,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F8,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F8,M$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$6=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F8,M$3)=1,AND(COUNTIF($F$4:F8,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F8,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F8,M$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
-      </x:c>
-      <x:c r="N9" s="83" t="n">
-        <x:f>IF(OR(N$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D9),COUNTIF($F$4:F8,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F8,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F8,N$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$7=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F8,N$3)=1,AND(COUNTIF($F$4:F8,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F8,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F8,N$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
-      </x:c>
-      <x:c r="O9" s="83" t="n">
-        <x:f>IF(OR(O$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D9),COUNTIF($F$4:F8,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F8,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F8,O$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$8=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F8,O$3)=1,AND(COUNTIF($F$4:F8,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F8,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F8,O$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
-        <x:v>-9999</x:v>
+      <x:c r="L9" s="83" t="str">
+        <x:f>IF(OR(L$3="",$A9=""),"",IF(W9=1,100+IF('キャディ条件'!$H$5=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F8,L$3)=1,AND(COUNTIF($F$4:F8,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F8,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F8,L$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
+      </x:c>
+      <x:c r="M9" s="83" t="str">
+        <x:f>IF(OR(M$3="",$A9=""),"",IF(X9=1,100+IF('キャディ条件'!$H$6=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F8,M$3)=1,AND(COUNTIF($F$4:F8,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F8,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F8,M$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
+      </x:c>
+      <x:c r="N9" s="83" t="str">
+        <x:f>IF(OR(N$3="",$A9=""),"",IF(Y9=1,100+IF('キャディ条件'!$H$7=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F8,N$3)=1,AND(COUNTIF($F$4:F8,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F8,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F8,N$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
+      </x:c>
+      <x:c r="O9" s="83" t="str">
+        <x:f>IF(OR(O$3="",$A9=""),"",IF(Z9=1,100+IF('キャディ条件'!$H$8=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F8,O$3)=1,AND(COUNTIF($F$4:F8,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F8,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F8,O$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P9" s="83" t="n">
-        <x:f>IF(OR(P$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D9),COUNTIF($F$4:F8,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F8,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F8,P$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$9=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F8,P$3)=1,AND(COUNTIF($F$4:F8,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F8,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F8,P$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A9=""),"",IF(AA9=1,100+IF('キャディ条件'!$H$9=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F8,P$3)=1,AND(COUNTIF($F$4:F8,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F8,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F8,P$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
         <x:v>96</x:v>
       </x:c>
       <x:c r="Q9" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D9),COUNTIF($F$4:F8,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F8,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F8,Q$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$10=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F8,Q$3)=1,AND(COUNTIF($F$4:F8,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F8,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F8,Q$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A9=""),"",IF(AB9=1,100+IF('キャディ条件'!$H$10=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F8,Q$3)=1,AND(COUNTIF($F$4:F8,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F8,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F8,Q$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R9" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D9),COUNTIF($F$4:F8,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F8,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F8,R$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$11=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F8,R$3)=1,AND(COUNTIF($F$4:F8,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F8,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F8,R$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A9=""),"",IF(AC9=1,100+IF('キャディ条件'!$H$11=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F8,R$3)=1,AND(COUNTIF($F$4:F8,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F8,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F8,R$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S9" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D9),COUNTIF($F$4:F8,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F8,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F8,S$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$12=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F8,S$3)=1,AND(COUNTIF($F$4:F8,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F8,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F8,S$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A9=""),"",IF(AD9=1,100+IF('キャディ条件'!$H$12=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F8,S$3)=1,AND(COUNTIF($F$4:F8,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F8,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F8,S$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T9" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D9),COUNTIF($F$4:F8,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F8,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F8,T$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$13=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F8,T$3)=1,AND(COUNTIF($F$4:F8,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F8,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F8,T$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A9=""),"",IF(AE9=1,100+IF('キャディ条件'!$H$13=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F8,T$3)=1,AND(COUNTIF($F$4:F8,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F8,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F8,T$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U9" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B9,2)&lt;=5)),$C9&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D9),COUNTIF($F$4:F8,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F8,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F8,U$3,$I$4:I8,"&gt;"&amp;$B9)=0),100+IF('キャディ条件'!$H$14=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F8,U$3)=1,AND(COUNTIF($F$4:F8,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F8,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F8,U$3,$C$4:C8,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A9=""),"",IF(AF9=1,100+IF('キャディ条件'!$H$14=$C9,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F8,U$3)=1,AND(COUNTIF($F$4:F8,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$10:$A$19,"&lt;&gt;",'ラウンド入力'!$B$10:$B$19,"&gt;="&amp;($B9+$E9/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$10:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$10:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C9=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F8,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F8,U$3,$C$4:C8,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V9" s="74" t="n">
         <x:f>IF($A9="","",IF($J9="人数希望一致",1,0))</x:f>
         <x:v>0</x:v>
       </x:c>
+      <x:c r="W9" s="202" t="n">
+        <x:f>IF(OR(L$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$5,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C9&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D9),COUNTIF($F$4:F8,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F8,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F8,L$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X9" s="203" t="n">
+        <x:f>IF(OR(M$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$6,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C9&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D9),COUNTIF($F$4:F8,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F8,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F8,M$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y9" s="203" t="n">
+        <x:f>IF(OR(N$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$7,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C9&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D9),COUNTIF($F$4:F8,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F8,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F8,N$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z9" s="203" t="n">
+        <x:f>IF(OR(O$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$8,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C9&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D9),COUNTIF($F$4:F8,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F8,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F8,O$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA9" s="203" t="n">
+        <x:f>IF(OR(P$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$9,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C9&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D9),COUNTIF($F$4:F8,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F8,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F8,P$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB9" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$10,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C9&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D9),COUNTIF($F$4:F8,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F8,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F8,Q$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC9" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$11,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C9&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D9),COUNTIF($F$4:F8,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F8,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F8,R$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD9" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$12,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C9&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D9),COUNTIF($F$4:F8,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F8,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F8,S$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE9" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$13,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C9&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D9),COUNTIF($F$4:F8,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F8,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F8,T$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF9" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A9=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B9,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B9,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B9,1)&gt;='キャディ条件'!$Q$14,MOD($B9+$E9/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C9&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D9),COUNTIF($F$4:F8,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F8,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F8,U$3,$I$4:I8,"&gt;"&amp;$B9)=0),1,0))</x:f>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="73" t="str">
@@ -2603,7 +3288,7 @@
         <x:f>IF('ラウンド入力'!A10="","",IF('ラウンド入力'!E10="",'設定・説明'!$B$6,'ラウンド入力'!E10))</x:f>
       </x:c>
       <x:c r="F10" s="74" t="str">
-        <x:f>IF($A10="","",IF(COUNTIF(L10:U10,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L10:U10),L10:U10,0))))</x:f>
+        <x:f>IF($A10="","",IF(SUM(W10:AF10)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L10:U10),L10:U10,0))))</x:f>
       </x:c>
       <x:c r="G10" s="74" t="str">
         <x:f>IF(OR($F10="",$F10="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F10,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2621,37 +3306,67 @@
         <x:f>IF($A10="","",IF($F10="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L10" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D10),COUNTIF($F$4:F9,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F9,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F9,L$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$5=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F9,L$3)=1,AND(COUNTIF($F$4:F9,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F9,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F9,L$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A10=""),"",IF(W10=1,100+IF('キャディ条件'!$H$5=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F9,L$3)=1,AND(COUNTIF($F$4:F9,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F9,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F9,L$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M10" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D10),COUNTIF($F$4:F9,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F9,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F9,M$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$6=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F9,M$3)=1,AND(COUNTIF($F$4:F9,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F9,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F9,M$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A10=""),"",IF(X10=1,100+IF('キャディ条件'!$H$6=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F9,M$3)=1,AND(COUNTIF($F$4:F9,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F9,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F9,M$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N10" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D10),COUNTIF($F$4:F9,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F9,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F9,N$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$7=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F9,N$3)=1,AND(COUNTIF($F$4:F9,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F9,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F9,N$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A10=""),"",IF(Y10=1,100+IF('キャディ条件'!$H$7=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F9,N$3)=1,AND(COUNTIF($F$4:F9,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F9,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F9,N$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O10" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D10),COUNTIF($F$4:F9,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F9,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F9,O$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$8=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F9,O$3)=1,AND(COUNTIF($F$4:F9,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F9,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F9,O$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A10=""),"",IF(Z10=1,100+IF('キャディ条件'!$H$8=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F9,O$3)=1,AND(COUNTIF($F$4:F9,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F9,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F9,O$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P10" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D10),COUNTIF($F$4:F9,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F9,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F9,P$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$9=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F9,P$3)=1,AND(COUNTIF($F$4:F9,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F9,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F9,P$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A10=""),"",IF(AA10=1,100+IF('キャディ条件'!$H$9=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F9,P$3)=1,AND(COUNTIF($F$4:F9,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F9,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F9,P$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q10" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D10),COUNTIF($F$4:F9,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F9,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F9,Q$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$10=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F9,Q$3)=1,AND(COUNTIF($F$4:F9,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F9,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F9,Q$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A10=""),"",IF(AB10=1,100+IF('キャディ条件'!$H$10=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F9,Q$3)=1,AND(COUNTIF($F$4:F9,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F9,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F9,Q$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R10" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D10),COUNTIF($F$4:F9,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F9,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F9,R$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$11=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F9,R$3)=1,AND(COUNTIF($F$4:F9,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F9,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F9,R$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A10=""),"",IF(AC10=1,100+IF('キャディ条件'!$H$11=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F9,R$3)=1,AND(COUNTIF($F$4:F9,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F9,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F9,R$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S10" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D10),COUNTIF($F$4:F9,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F9,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F9,S$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$12=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F9,S$3)=1,AND(COUNTIF($F$4:F9,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F9,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F9,S$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A10=""),"",IF(AD10=1,100+IF('キャディ条件'!$H$12=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F9,S$3)=1,AND(COUNTIF($F$4:F9,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F9,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F9,S$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T10" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D10),COUNTIF($F$4:F9,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F9,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F9,T$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$13=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F9,T$3)=1,AND(COUNTIF($F$4:F9,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F9,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F9,T$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A10=""),"",IF(AE10=1,100+IF('キャディ条件'!$H$13=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F9,T$3)=1,AND(COUNTIF($F$4:F9,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F9,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F9,T$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U10" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B10,2)&lt;=5)),$C10&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D10),COUNTIF($F$4:F9,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F9,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F9,U$3,$I$4:I9,"&gt;"&amp;$B10)=0),100+IF('キャディ条件'!$H$14=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F9,U$3)=1,AND(COUNTIF($F$4:F9,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F9,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F9,U$3,$C$4:C9,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A10=""),"",IF(AF10=1,100+IF('キャディ条件'!$H$14=$C10,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F9,U$3)=1,AND(COUNTIF($F$4:F9,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$11:$A$19,"&lt;&gt;",'ラウンド入力'!$B$11:$B$19,"&gt;="&amp;($B10+$E10/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$11:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$11:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C10=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F9,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F9,U$3,$C$4:C9,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V10" s="74" t="str">
         <x:f>IF($A10="","",IF($J10="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W10" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$5,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C10&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D10),COUNTIF($F$4:F9,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F9,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F9,L$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X10" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$6,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C10&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D10),COUNTIF($F$4:F9,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F9,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F9,M$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y10" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$7,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C10&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D10),COUNTIF($F$4:F9,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F9,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F9,N$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z10" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$8,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C10&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D10),COUNTIF($F$4:F9,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F9,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F9,O$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA10" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$9,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C10&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D10),COUNTIF($F$4:F9,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F9,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F9,P$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB10" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$10,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C10&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D10),COUNTIF($F$4:F9,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F9,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F9,Q$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC10" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$11,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C10&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D10),COUNTIF($F$4:F9,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F9,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F9,R$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD10" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$12,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C10&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D10),COUNTIF($F$4:F9,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F9,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F9,S$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE10" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$13,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C10&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D10),COUNTIF($F$4:F9,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F9,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F9,T$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF10" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A10=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B10,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B10,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B10,1)&gt;='キャディ条件'!$Q$14,MOD($B10+$E10/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C10&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D10),COUNTIF($F$4:F9,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F9,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F9,U$3,$I$4:I9,"&gt;"&amp;$B10)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -2671,7 +3386,7 @@
         <x:f>IF('ラウンド入力'!A11="","",IF('ラウンド入力'!E11="",'設定・説明'!$B$6,'ラウンド入力'!E11))</x:f>
       </x:c>
       <x:c r="F11" s="74" t="str">
-        <x:f>IF($A11="","",IF(COUNTIF(L11:U11,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L11:U11),L11:U11,0))))</x:f>
+        <x:f>IF($A11="","",IF(SUM(W11:AF11)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L11:U11),L11:U11,0))))</x:f>
       </x:c>
       <x:c r="G11" s="74" t="str">
         <x:f>IF(OR($F11="",$F11="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F11,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2689,37 +3404,67 @@
         <x:f>IF($A11="","",IF($F11="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L11" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D11),COUNTIF($F$4:F10,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F10,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F10,L$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$5=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F10,L$3)=1,AND(COUNTIF($F$4:F10,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F10,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F10,L$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A11=""),"",IF(W11=1,100+IF('キャディ条件'!$H$5=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F10,L$3)=1,AND(COUNTIF($F$4:F10,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F10,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F10,L$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M11" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D11),COUNTIF($F$4:F10,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F10,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F10,M$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$6=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F10,M$3)=1,AND(COUNTIF($F$4:F10,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F10,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F10,M$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A11=""),"",IF(X11=1,100+IF('キャディ条件'!$H$6=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F10,M$3)=1,AND(COUNTIF($F$4:F10,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F10,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F10,M$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N11" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D11),COUNTIF($F$4:F10,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F10,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F10,N$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$7=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F10,N$3)=1,AND(COUNTIF($F$4:F10,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F10,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F10,N$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A11=""),"",IF(Y11=1,100+IF('キャディ条件'!$H$7=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F10,N$3)=1,AND(COUNTIF($F$4:F10,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F10,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F10,N$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O11" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D11),COUNTIF($F$4:F10,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F10,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F10,O$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$8=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F10,O$3)=1,AND(COUNTIF($F$4:F10,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F10,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F10,O$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A11=""),"",IF(Z11=1,100+IF('キャディ条件'!$H$8=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F10,O$3)=1,AND(COUNTIF($F$4:F10,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F10,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F10,O$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P11" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D11),COUNTIF($F$4:F10,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F10,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F10,P$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$9=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F10,P$3)=1,AND(COUNTIF($F$4:F10,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F10,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F10,P$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A11=""),"",IF(AA11=1,100+IF('キャディ条件'!$H$9=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F10,P$3)=1,AND(COUNTIF($F$4:F10,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F10,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F10,P$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q11" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D11),COUNTIF($F$4:F10,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F10,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F10,Q$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$10=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F10,Q$3)=1,AND(COUNTIF($F$4:F10,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F10,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F10,Q$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A11=""),"",IF(AB11=1,100+IF('キャディ条件'!$H$10=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F10,Q$3)=1,AND(COUNTIF($F$4:F10,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F10,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F10,Q$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R11" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D11),COUNTIF($F$4:F10,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F10,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F10,R$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$11=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F10,R$3)=1,AND(COUNTIF($F$4:F10,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F10,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F10,R$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A11=""),"",IF(AC11=1,100+IF('キャディ条件'!$H$11=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F10,R$3)=1,AND(COUNTIF($F$4:F10,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F10,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F10,R$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S11" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D11),COUNTIF($F$4:F10,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F10,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F10,S$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$12=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F10,S$3)=1,AND(COUNTIF($F$4:F10,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F10,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F10,S$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A11=""),"",IF(AD11=1,100+IF('キャディ条件'!$H$12=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F10,S$3)=1,AND(COUNTIF($F$4:F10,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F10,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F10,S$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T11" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D11),COUNTIF($F$4:F10,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F10,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F10,T$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$13=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F10,T$3)=1,AND(COUNTIF($F$4:F10,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F10,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F10,T$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A11=""),"",IF(AE11=1,100+IF('キャディ条件'!$H$13=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F10,T$3)=1,AND(COUNTIF($F$4:F10,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F10,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F10,T$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U11" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B11,2)&lt;=5)),$C11&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D11),COUNTIF($F$4:F10,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F10,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F10,U$3,$I$4:I10,"&gt;"&amp;$B11)=0),100+IF('キャディ条件'!$H$14=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F10,U$3)=1,AND(COUNTIF($F$4:F10,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F10,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F10,U$3,$C$4:C10,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A11=""),"",IF(AF11=1,100+IF('キャディ条件'!$H$14=$C11,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F10,U$3)=1,AND(COUNTIF($F$4:F10,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$12:$A$19,"&lt;&gt;",'ラウンド入力'!$B$12:$B$19,"&gt;="&amp;($B11+$E11/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$12:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$12:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C11=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F10,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F10,U$3,$C$4:C10,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V11" s="74" t="str">
         <x:f>IF($A11="","",IF($J11="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W11" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$5,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C11&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D11),COUNTIF($F$4:F10,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F10,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F10,L$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X11" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$6,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C11&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D11),COUNTIF($F$4:F10,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F10,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F10,M$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y11" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$7,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C11&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D11),COUNTIF($F$4:F10,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F10,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F10,N$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z11" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$8,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C11&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D11),COUNTIF($F$4:F10,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F10,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F10,O$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA11" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$9,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C11&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D11),COUNTIF($F$4:F10,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F10,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F10,P$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB11" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$10,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C11&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D11),COUNTIF($F$4:F10,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F10,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F10,Q$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC11" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$11,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C11&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D11),COUNTIF($F$4:F10,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F10,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F10,R$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD11" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$12,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C11&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D11),COUNTIF($F$4:F10,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F10,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F10,S$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE11" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$13,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C11&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D11),COUNTIF($F$4:F10,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F10,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F10,T$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF11" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A11=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B11,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B11,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B11,1)&gt;='キャディ条件'!$Q$14,MOD($B11+$E11/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C11&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D11),COUNTIF($F$4:F10,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F10,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F10,U$3,$I$4:I10,"&gt;"&amp;$B11)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2739,7 +3484,7 @@
         <x:f>IF('ラウンド入力'!A12="","",IF('ラウンド入力'!E12="",'設定・説明'!$B$6,'ラウンド入力'!E12))</x:f>
       </x:c>
       <x:c r="F12" s="74" t="str">
-        <x:f>IF($A12="","",IF(COUNTIF(L12:U12,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L12:U12),L12:U12,0))))</x:f>
+        <x:f>IF($A12="","",IF(SUM(W12:AF12)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L12:U12),L12:U12,0))))</x:f>
       </x:c>
       <x:c r="G12" s="74" t="str">
         <x:f>IF(OR($F12="",$F12="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F12,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2757,37 +3502,67 @@
         <x:f>IF($A12="","",IF($F12="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L12" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D12),COUNTIF($F$4:F11,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F11,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F11,L$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$5=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F11,L$3)=1,AND(COUNTIF($F$4:F11,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F11,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F11,L$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A12=""),"",IF(W12=1,100+IF('キャディ条件'!$H$5=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F11,L$3)=1,AND(COUNTIF($F$4:F11,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F11,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F11,L$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M12" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D12),COUNTIF($F$4:F11,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F11,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F11,M$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$6=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F11,M$3)=1,AND(COUNTIF($F$4:F11,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F11,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F11,M$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A12=""),"",IF(X12=1,100+IF('キャディ条件'!$H$6=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F11,M$3)=1,AND(COUNTIF($F$4:F11,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F11,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F11,M$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N12" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D12),COUNTIF($F$4:F11,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F11,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F11,N$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$7=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F11,N$3)=1,AND(COUNTIF($F$4:F11,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F11,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F11,N$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A12=""),"",IF(Y12=1,100+IF('キャディ条件'!$H$7=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F11,N$3)=1,AND(COUNTIF($F$4:F11,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F11,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F11,N$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O12" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D12),COUNTIF($F$4:F11,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F11,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F11,O$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$8=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F11,O$3)=1,AND(COUNTIF($F$4:F11,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F11,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F11,O$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A12=""),"",IF(Z12=1,100+IF('キャディ条件'!$H$8=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F11,O$3)=1,AND(COUNTIF($F$4:F11,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F11,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F11,O$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P12" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D12),COUNTIF($F$4:F11,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F11,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F11,P$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$9=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F11,P$3)=1,AND(COUNTIF($F$4:F11,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F11,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F11,P$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A12=""),"",IF(AA12=1,100+IF('キャディ条件'!$H$9=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F11,P$3)=1,AND(COUNTIF($F$4:F11,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F11,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F11,P$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q12" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D12),COUNTIF($F$4:F11,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F11,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F11,Q$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$10=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F11,Q$3)=1,AND(COUNTIF($F$4:F11,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F11,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F11,Q$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A12=""),"",IF(AB12=1,100+IF('キャディ条件'!$H$10=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F11,Q$3)=1,AND(COUNTIF($F$4:F11,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F11,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F11,Q$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R12" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D12),COUNTIF($F$4:F11,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F11,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F11,R$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$11=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F11,R$3)=1,AND(COUNTIF($F$4:F11,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F11,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F11,R$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A12=""),"",IF(AC12=1,100+IF('キャディ条件'!$H$11=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F11,R$3)=1,AND(COUNTIF($F$4:F11,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F11,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F11,R$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S12" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D12),COUNTIF($F$4:F11,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F11,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F11,S$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$12=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F11,S$3)=1,AND(COUNTIF($F$4:F11,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F11,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F11,S$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A12=""),"",IF(AD12=1,100+IF('キャディ条件'!$H$12=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F11,S$3)=1,AND(COUNTIF($F$4:F11,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F11,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F11,S$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T12" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D12),COUNTIF($F$4:F11,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F11,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F11,T$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$13=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F11,T$3)=1,AND(COUNTIF($F$4:F11,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F11,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F11,T$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A12=""),"",IF(AE12=1,100+IF('キャディ条件'!$H$13=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F11,T$3)=1,AND(COUNTIF($F$4:F11,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F11,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F11,T$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U12" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B12,2)&lt;=5)),$C12&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D12),COUNTIF($F$4:F11,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F11,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F11,U$3,$I$4:I11,"&gt;"&amp;$B12)=0),100+IF('キャディ条件'!$H$14=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F11,U$3)=1,AND(COUNTIF($F$4:F11,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F11,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F11,U$3,$C$4:C11,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A12=""),"",IF(AF12=1,100+IF('キャディ条件'!$H$14=$C12,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F11,U$3)=1,AND(COUNTIF($F$4:F11,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$13:$A$19,"&lt;&gt;",'ラウンド入力'!$B$13:$B$19,"&gt;="&amp;($B12+$E12/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$13:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$13:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C12=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F11,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F11,U$3,$C$4:C11,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V12" s="74" t="str">
         <x:f>IF($A12="","",IF($J12="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W12" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$5,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C12&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D12),COUNTIF($F$4:F11,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F11,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F11,L$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X12" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$6,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C12&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D12),COUNTIF($F$4:F11,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F11,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F11,M$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y12" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$7,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C12&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D12),COUNTIF($F$4:F11,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F11,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F11,N$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z12" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$8,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C12&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D12),COUNTIF($F$4:F11,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F11,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F11,O$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA12" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$9,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C12&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D12),COUNTIF($F$4:F11,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F11,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F11,P$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB12" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$10,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C12&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D12),COUNTIF($F$4:F11,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F11,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F11,Q$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC12" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$11,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C12&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D12),COUNTIF($F$4:F11,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F11,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F11,R$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD12" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$12,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C12&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D12),COUNTIF($F$4:F11,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F11,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F11,S$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE12" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$13,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C12&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D12),COUNTIF($F$4:F11,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F11,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F11,T$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF12" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A12=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B12,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B12,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B12,1)&gt;='キャディ条件'!$Q$14,MOD($B12+$E12/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C12&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D12),COUNTIF($F$4:F11,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F11,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F11,U$3,$I$4:I11,"&gt;"&amp;$B12)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2807,7 +3582,7 @@
         <x:f>IF('ラウンド入力'!A13="","",IF('ラウンド入力'!E13="",'設定・説明'!$B$6,'ラウンド入力'!E13))</x:f>
       </x:c>
       <x:c r="F13" s="74" t="str">
-        <x:f>IF($A13="","",IF(COUNTIF(L13:U13,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L13:U13),L13:U13,0))))</x:f>
+        <x:f>IF($A13="","",IF(SUM(W13:AF13)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L13:U13),L13:U13,0))))</x:f>
       </x:c>
       <x:c r="G13" s="74" t="str">
         <x:f>IF(OR($F13="",$F13="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F13,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2825,37 +3600,67 @@
         <x:f>IF($A13="","",IF($F13="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L13" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D13),COUNTIF($F$4:F12,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F12,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F12,L$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$5=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F12,L$3)=1,AND(COUNTIF($F$4:F12,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F12,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F12,L$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A13=""),"",IF(W13=1,100+IF('キャディ条件'!$H$5=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F12,L$3)=1,AND(COUNTIF($F$4:F12,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F12,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F12,L$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M13" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D13),COUNTIF($F$4:F12,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F12,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F12,M$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$6=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F12,M$3)=1,AND(COUNTIF($F$4:F12,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F12,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F12,M$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A13=""),"",IF(X13=1,100+IF('キャディ条件'!$H$6=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F12,M$3)=1,AND(COUNTIF($F$4:F12,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F12,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F12,M$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N13" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D13),COUNTIF($F$4:F12,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F12,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F12,N$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$7=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F12,N$3)=1,AND(COUNTIF($F$4:F12,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F12,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F12,N$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A13=""),"",IF(Y13=1,100+IF('キャディ条件'!$H$7=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F12,N$3)=1,AND(COUNTIF($F$4:F12,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F12,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F12,N$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O13" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D13),COUNTIF($F$4:F12,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F12,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F12,O$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$8=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F12,O$3)=1,AND(COUNTIF($F$4:F12,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F12,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F12,O$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A13=""),"",IF(Z13=1,100+IF('キャディ条件'!$H$8=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F12,O$3)=1,AND(COUNTIF($F$4:F12,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F12,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F12,O$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P13" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D13),COUNTIF($F$4:F12,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F12,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F12,P$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$9=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F12,P$3)=1,AND(COUNTIF($F$4:F12,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F12,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F12,P$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A13=""),"",IF(AA13=1,100+IF('キャディ条件'!$H$9=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F12,P$3)=1,AND(COUNTIF($F$4:F12,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F12,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F12,P$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q13" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D13),COUNTIF($F$4:F12,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F12,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F12,Q$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$10=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F12,Q$3)=1,AND(COUNTIF($F$4:F12,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F12,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F12,Q$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A13=""),"",IF(AB13=1,100+IF('キャディ条件'!$H$10=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F12,Q$3)=1,AND(COUNTIF($F$4:F12,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F12,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F12,Q$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R13" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D13),COUNTIF($F$4:F12,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F12,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F12,R$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$11=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F12,R$3)=1,AND(COUNTIF($F$4:F12,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F12,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F12,R$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A13=""),"",IF(AC13=1,100+IF('キャディ条件'!$H$11=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F12,R$3)=1,AND(COUNTIF($F$4:F12,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F12,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F12,R$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S13" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D13),COUNTIF($F$4:F12,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F12,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F12,S$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$12=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F12,S$3)=1,AND(COUNTIF($F$4:F12,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F12,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F12,S$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A13=""),"",IF(AD13=1,100+IF('キャディ条件'!$H$12=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F12,S$3)=1,AND(COUNTIF($F$4:F12,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F12,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F12,S$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T13" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D13),COUNTIF($F$4:F12,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F12,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F12,T$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$13=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F12,T$3)=1,AND(COUNTIF($F$4:F12,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F12,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F12,T$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A13=""),"",IF(AE13=1,100+IF('キャディ条件'!$H$13=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F12,T$3)=1,AND(COUNTIF($F$4:F12,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F12,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F12,T$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U13" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B13,2)&lt;=5)),$C13&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D13),COUNTIF($F$4:F12,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F12,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F12,U$3,$I$4:I12,"&gt;"&amp;$B13)=0),100+IF('キャディ条件'!$H$14=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F12,U$3)=1,AND(COUNTIF($F$4:F12,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F12,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F12,U$3,$C$4:C12,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A13=""),"",IF(AF13=1,100+IF('キャディ条件'!$H$14=$C13,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F12,U$3)=1,AND(COUNTIF($F$4:F12,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$14:$A$19,"&lt;&gt;",'ラウンド入力'!$B$14:$B$19,"&gt;="&amp;($B13+$E13/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$14:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$14:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C13=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F12,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F12,U$3,$C$4:C12,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V13" s="74" t="str">
         <x:f>IF($A13="","",IF($J13="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W13" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$5,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C13&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D13),COUNTIF($F$4:F12,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F12,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F12,L$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X13" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$6,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C13&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D13),COUNTIF($F$4:F12,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F12,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F12,M$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y13" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$7,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C13&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D13),COUNTIF($F$4:F12,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F12,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F12,N$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z13" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$8,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C13&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D13),COUNTIF($F$4:F12,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F12,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F12,O$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA13" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$9,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C13&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D13),COUNTIF($F$4:F12,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F12,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F12,P$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB13" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$10,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C13&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D13),COUNTIF($F$4:F12,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F12,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F12,Q$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC13" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$11,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C13&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D13),COUNTIF($F$4:F12,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F12,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F12,R$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD13" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$12,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C13&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D13),COUNTIF($F$4:F12,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F12,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F12,S$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE13" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$13,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C13&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D13),COUNTIF($F$4:F12,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F12,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F12,T$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF13" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A13=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B13,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B13,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B13,1)&gt;='キャディ条件'!$Q$14,MOD($B13+$E13/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C13&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D13),COUNTIF($F$4:F12,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F12,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F12,U$3,$I$4:I12,"&gt;"&amp;$B13)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2875,7 +3680,7 @@
         <x:f>IF('ラウンド入力'!A14="","",IF('ラウンド入力'!E14="",'設定・説明'!$B$6,'ラウンド入力'!E14))</x:f>
       </x:c>
       <x:c r="F14" s="74" t="str">
-        <x:f>IF($A14="","",IF(COUNTIF(L14:U14,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L14:U14),L14:U14,0))))</x:f>
+        <x:f>IF($A14="","",IF(SUM(W14:AF14)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L14:U14),L14:U14,0))))</x:f>
       </x:c>
       <x:c r="G14" s="74" t="str">
         <x:f>IF(OR($F14="",$F14="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F14,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2893,37 +3698,67 @@
         <x:f>IF($A14="","",IF($F14="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L14" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D14),COUNTIF($F$4:F13,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F13,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F13,L$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$5=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F13,L$3)=1,AND(COUNTIF($F$4:F13,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F13,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F13,L$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A14=""),"",IF(W14=1,100+IF('キャディ条件'!$H$5=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F13,L$3)=1,AND(COUNTIF($F$4:F13,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F13,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F13,L$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M14" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D14),COUNTIF($F$4:F13,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F13,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F13,M$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$6=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F13,M$3)=1,AND(COUNTIF($F$4:F13,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F13,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F13,M$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A14=""),"",IF(X14=1,100+IF('キャディ条件'!$H$6=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F13,M$3)=1,AND(COUNTIF($F$4:F13,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F13,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F13,M$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N14" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D14),COUNTIF($F$4:F13,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F13,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F13,N$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$7=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F13,N$3)=1,AND(COUNTIF($F$4:F13,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F13,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F13,N$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A14=""),"",IF(Y14=1,100+IF('キャディ条件'!$H$7=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F13,N$3)=1,AND(COUNTIF($F$4:F13,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F13,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F13,N$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O14" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D14),COUNTIF($F$4:F13,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F13,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F13,O$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$8=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F13,O$3)=1,AND(COUNTIF($F$4:F13,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F13,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F13,O$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A14=""),"",IF(Z14=1,100+IF('キャディ条件'!$H$8=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F13,O$3)=1,AND(COUNTIF($F$4:F13,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F13,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F13,O$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P14" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D14),COUNTIF($F$4:F13,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F13,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F13,P$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$9=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F13,P$3)=1,AND(COUNTIF($F$4:F13,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F13,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F13,P$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A14=""),"",IF(AA14=1,100+IF('キャディ条件'!$H$9=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F13,P$3)=1,AND(COUNTIF($F$4:F13,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F13,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F13,P$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q14" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D14),COUNTIF($F$4:F13,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F13,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F13,Q$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$10=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F13,Q$3)=1,AND(COUNTIF($F$4:F13,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F13,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F13,Q$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A14=""),"",IF(AB14=1,100+IF('キャディ条件'!$H$10=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F13,Q$3)=1,AND(COUNTIF($F$4:F13,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F13,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F13,Q$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R14" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D14),COUNTIF($F$4:F13,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F13,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F13,R$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$11=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F13,R$3)=1,AND(COUNTIF($F$4:F13,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F13,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F13,R$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A14=""),"",IF(AC14=1,100+IF('キャディ条件'!$H$11=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F13,R$3)=1,AND(COUNTIF($F$4:F13,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F13,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F13,R$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S14" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D14),COUNTIF($F$4:F13,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F13,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F13,S$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$12=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F13,S$3)=1,AND(COUNTIF($F$4:F13,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F13,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F13,S$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A14=""),"",IF(AD14=1,100+IF('キャディ条件'!$H$12=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F13,S$3)=1,AND(COUNTIF($F$4:F13,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F13,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F13,S$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T14" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D14),COUNTIF($F$4:F13,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F13,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F13,T$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$13=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F13,T$3)=1,AND(COUNTIF($F$4:F13,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F13,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F13,T$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A14=""),"",IF(AE14=1,100+IF('キャディ条件'!$H$13=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F13,T$3)=1,AND(COUNTIF($F$4:F13,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F13,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F13,T$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U14" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B14,2)&lt;=5)),$C14&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D14),COUNTIF($F$4:F13,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F13,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F13,U$3,$I$4:I13,"&gt;"&amp;$B14)=0),100+IF('キャディ条件'!$H$14=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F13,U$3)=1,AND(COUNTIF($F$4:F13,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F13,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F13,U$3,$C$4:C13,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A14=""),"",IF(AF14=1,100+IF('キャディ条件'!$H$14=$C14,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F13,U$3)=1,AND(COUNTIF($F$4:F13,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$15:$A$19,"&lt;&gt;",'ラウンド入力'!$B$15:$B$19,"&gt;="&amp;($B14+$E14/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$15:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$15:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C14=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F13,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F13,U$3,$C$4:C13,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V14" s="74" t="str">
         <x:f>IF($A14="","",IF($J14="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W14" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$5,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C14&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D14),COUNTIF($F$4:F13,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F13,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F13,L$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X14" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$6,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C14&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D14),COUNTIF($F$4:F13,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F13,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F13,M$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y14" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$7,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C14&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D14),COUNTIF($F$4:F13,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F13,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F13,N$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z14" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$8,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C14&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D14),COUNTIF($F$4:F13,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F13,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F13,O$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA14" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$9,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C14&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D14),COUNTIF($F$4:F13,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F13,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F13,P$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB14" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$10,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C14&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D14),COUNTIF($F$4:F13,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F13,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F13,Q$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC14" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$11,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C14&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D14),COUNTIF($F$4:F13,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F13,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F13,R$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD14" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$12,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C14&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D14),COUNTIF($F$4:F13,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F13,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F13,S$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE14" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$13,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C14&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D14),COUNTIF($F$4:F13,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F13,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F13,T$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF14" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A14=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B14,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B14,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B14,1)&gt;='キャディ条件'!$Q$14,MOD($B14+$E14/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C14&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D14),COUNTIF($F$4:F13,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F13,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F13,U$3,$I$4:I13,"&gt;"&amp;$B14)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2943,7 +3778,7 @@
         <x:f>IF('ラウンド入力'!A15="","",IF('ラウンド入力'!E15="",'設定・説明'!$B$6,'ラウンド入力'!E15))</x:f>
       </x:c>
       <x:c r="F15" s="74" t="str">
-        <x:f>IF($A15="","",IF(COUNTIF(L15:U15,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L15:U15),L15:U15,0))))</x:f>
+        <x:f>IF($A15="","",IF(SUM(W15:AF15)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L15:U15),L15:U15,0))))</x:f>
       </x:c>
       <x:c r="G15" s="74" t="str">
         <x:f>IF(OR($F15="",$F15="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F15,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -2961,37 +3796,67 @@
         <x:f>IF($A15="","",IF($F15="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L15" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D15),COUNTIF($F$4:F14,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F14,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F14,L$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$5=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F14,L$3)=1,AND(COUNTIF($F$4:F14,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F14,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F14,L$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A15=""),"",IF(W15=1,100+IF('キャディ条件'!$H$5=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F14,L$3)=1,AND(COUNTIF($F$4:F14,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F14,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F14,L$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M15" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D15),COUNTIF($F$4:F14,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F14,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F14,M$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$6=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F14,M$3)=1,AND(COUNTIF($F$4:F14,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F14,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F14,M$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A15=""),"",IF(X15=1,100+IF('キャディ条件'!$H$6=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F14,M$3)=1,AND(COUNTIF($F$4:F14,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F14,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F14,M$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N15" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D15),COUNTIF($F$4:F14,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F14,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F14,N$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$7=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F14,N$3)=1,AND(COUNTIF($F$4:F14,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F14,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F14,N$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A15=""),"",IF(Y15=1,100+IF('キャディ条件'!$H$7=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F14,N$3)=1,AND(COUNTIF($F$4:F14,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F14,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F14,N$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O15" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D15),COUNTIF($F$4:F14,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F14,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F14,O$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$8=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F14,O$3)=1,AND(COUNTIF($F$4:F14,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F14,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F14,O$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A15=""),"",IF(Z15=1,100+IF('キャディ条件'!$H$8=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F14,O$3)=1,AND(COUNTIF($F$4:F14,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F14,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F14,O$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P15" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D15),COUNTIF($F$4:F14,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F14,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F14,P$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$9=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F14,P$3)=1,AND(COUNTIF($F$4:F14,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F14,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F14,P$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A15=""),"",IF(AA15=1,100+IF('キャディ条件'!$H$9=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F14,P$3)=1,AND(COUNTIF($F$4:F14,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F14,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F14,P$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q15" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D15),COUNTIF($F$4:F14,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F14,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F14,Q$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$10=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F14,Q$3)=1,AND(COUNTIF($F$4:F14,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F14,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F14,Q$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A15=""),"",IF(AB15=1,100+IF('キャディ条件'!$H$10=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F14,Q$3)=1,AND(COUNTIF($F$4:F14,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F14,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F14,Q$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R15" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D15),COUNTIF($F$4:F14,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F14,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F14,R$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$11=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F14,R$3)=1,AND(COUNTIF($F$4:F14,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F14,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F14,R$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A15=""),"",IF(AC15=1,100+IF('キャディ条件'!$H$11=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F14,R$3)=1,AND(COUNTIF($F$4:F14,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F14,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F14,R$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S15" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D15),COUNTIF($F$4:F14,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F14,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F14,S$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$12=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F14,S$3)=1,AND(COUNTIF($F$4:F14,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F14,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F14,S$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A15=""),"",IF(AD15=1,100+IF('キャディ条件'!$H$12=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F14,S$3)=1,AND(COUNTIF($F$4:F14,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F14,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F14,S$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T15" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D15),COUNTIF($F$4:F14,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F14,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F14,T$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$13=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F14,T$3)=1,AND(COUNTIF($F$4:F14,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F14,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F14,T$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A15=""),"",IF(AE15=1,100+IF('キャディ条件'!$H$13=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F14,T$3)=1,AND(COUNTIF($F$4:F14,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F14,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F14,T$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U15" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B15,2)&lt;=5)),$C15&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D15),COUNTIF($F$4:F14,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F14,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F14,U$3,$I$4:I14,"&gt;"&amp;$B15)=0),100+IF('キャディ条件'!$H$14=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F14,U$3)=1,AND(COUNTIF($F$4:F14,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F14,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F14,U$3,$C$4:C14,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A15=""),"",IF(AF15=1,100+IF('キャディ条件'!$H$14=$C15,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F14,U$3)=1,AND(COUNTIF($F$4:F14,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$16:$A$19,"&lt;&gt;",'ラウンド入力'!$B$16:$B$19,"&gt;="&amp;($B15+$E15/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$16:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$16:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C15=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F14,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F14,U$3,$C$4:C14,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V15" s="74" t="str">
         <x:f>IF($A15="","",IF($J15="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W15" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$5,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C15&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D15),COUNTIF($F$4:F14,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F14,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F14,L$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X15" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$6,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C15&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D15),COUNTIF($F$4:F14,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F14,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F14,M$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y15" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$7,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C15&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D15),COUNTIF($F$4:F14,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F14,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F14,N$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z15" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$8,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C15&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D15),COUNTIF($F$4:F14,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F14,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F14,O$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA15" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$9,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C15&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D15),COUNTIF($F$4:F14,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F14,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F14,P$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB15" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$10,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C15&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D15),COUNTIF($F$4:F14,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F14,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F14,Q$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC15" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$11,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C15&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D15),COUNTIF($F$4:F14,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F14,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F14,R$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD15" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$12,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C15&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D15),COUNTIF($F$4:F14,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F14,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F14,S$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE15" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$13,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C15&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D15),COUNTIF($F$4:F14,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F14,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F14,T$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF15" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A15=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B15,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B15,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B15,1)&gt;='キャディ条件'!$Q$14,MOD($B15+$E15/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C15&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D15),COUNTIF($F$4:F14,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F14,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F14,U$3,$I$4:I14,"&gt;"&amp;$B15)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3011,7 +3876,7 @@
         <x:f>IF('ラウンド入力'!A16="","",IF('ラウンド入力'!E16="",'設定・説明'!$B$6,'ラウンド入力'!E16))</x:f>
       </x:c>
       <x:c r="F16" s="74" t="str">
-        <x:f>IF($A16="","",IF(COUNTIF(L16:U16,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L16:U16),L16:U16,0))))</x:f>
+        <x:f>IF($A16="","",IF(SUM(W16:AF16)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L16:U16),L16:U16,0))))</x:f>
       </x:c>
       <x:c r="G16" s="74" t="str">
         <x:f>IF(OR($F16="",$F16="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F16,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -3029,37 +3894,67 @@
         <x:f>IF($A16="","",IF($F16="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L16" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D16),COUNTIF($F$4:F15,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F15,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F15,L$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$5=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F15,L$3)=1,AND(COUNTIF($F$4:F15,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F15,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F15,L$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A16=""),"",IF(W16=1,100+IF('キャディ条件'!$H$5=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F15,L$3)=1,AND(COUNTIF($F$4:F15,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F15,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F15,L$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M16" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D16),COUNTIF($F$4:F15,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F15,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F15,M$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$6=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F15,M$3)=1,AND(COUNTIF($F$4:F15,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F15,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F15,M$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A16=""),"",IF(X16=1,100+IF('キャディ条件'!$H$6=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F15,M$3)=1,AND(COUNTIF($F$4:F15,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F15,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F15,M$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N16" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D16),COUNTIF($F$4:F15,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F15,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F15,N$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$7=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F15,N$3)=1,AND(COUNTIF($F$4:F15,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F15,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F15,N$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A16=""),"",IF(Y16=1,100+IF('キャディ条件'!$H$7=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F15,N$3)=1,AND(COUNTIF($F$4:F15,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F15,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F15,N$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O16" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D16),COUNTIF($F$4:F15,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F15,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F15,O$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$8=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F15,O$3)=1,AND(COUNTIF($F$4:F15,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F15,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F15,O$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A16=""),"",IF(Z16=1,100+IF('キャディ条件'!$H$8=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F15,O$3)=1,AND(COUNTIF($F$4:F15,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F15,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F15,O$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P16" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D16),COUNTIF($F$4:F15,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F15,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F15,P$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$9=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F15,P$3)=1,AND(COUNTIF($F$4:F15,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F15,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F15,P$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A16=""),"",IF(AA16=1,100+IF('キャディ条件'!$H$9=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F15,P$3)=1,AND(COUNTIF($F$4:F15,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F15,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F15,P$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q16" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D16),COUNTIF($F$4:F15,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F15,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F15,Q$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$10=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F15,Q$3)=1,AND(COUNTIF($F$4:F15,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F15,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F15,Q$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A16=""),"",IF(AB16=1,100+IF('キャディ条件'!$H$10=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F15,Q$3)=1,AND(COUNTIF($F$4:F15,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F15,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F15,Q$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R16" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D16),COUNTIF($F$4:F15,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F15,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F15,R$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$11=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F15,R$3)=1,AND(COUNTIF($F$4:F15,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F15,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F15,R$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A16=""),"",IF(AC16=1,100+IF('キャディ条件'!$H$11=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F15,R$3)=1,AND(COUNTIF($F$4:F15,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F15,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F15,R$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S16" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D16),COUNTIF($F$4:F15,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F15,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F15,S$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$12=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F15,S$3)=1,AND(COUNTIF($F$4:F15,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F15,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F15,S$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A16=""),"",IF(AD16=1,100+IF('キャディ条件'!$H$12=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F15,S$3)=1,AND(COUNTIF($F$4:F15,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F15,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F15,S$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T16" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D16),COUNTIF($F$4:F15,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F15,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F15,T$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$13=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F15,T$3)=1,AND(COUNTIF($F$4:F15,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F15,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F15,T$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A16=""),"",IF(AE16=1,100+IF('キャディ条件'!$H$13=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F15,T$3)=1,AND(COUNTIF($F$4:F15,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F15,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F15,T$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U16" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B16,2)&lt;=5)),$C16&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D16),COUNTIF($F$4:F15,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F15,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F15,U$3,$I$4:I15,"&gt;"&amp;$B16)=0),100+IF('キャディ条件'!$H$14=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F15,U$3)=1,AND(COUNTIF($F$4:F15,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F15,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F15,U$3,$C$4:C15,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A16=""),"",IF(AF16=1,100+IF('キャディ条件'!$H$14=$C16,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F15,U$3)=1,AND(COUNTIF($F$4:F15,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$17:$A$19,"&lt;&gt;",'ラウンド入力'!$B$17:$B$19,"&gt;="&amp;($B16+$E16/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$17:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$17:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C16=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F15,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F15,U$3,$C$4:C15,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V16" s="74" t="str">
         <x:f>IF($A16="","",IF($J16="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W16" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$5,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C16&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D16),COUNTIF($F$4:F15,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F15,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F15,L$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X16" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$6,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C16&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D16),COUNTIF($F$4:F15,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F15,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F15,M$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y16" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$7,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C16&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D16),COUNTIF($F$4:F15,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F15,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F15,N$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z16" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$8,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C16&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D16),COUNTIF($F$4:F15,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F15,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F15,O$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA16" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$9,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C16&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D16),COUNTIF($F$4:F15,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F15,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F15,P$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB16" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$10,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C16&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D16),COUNTIF($F$4:F15,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F15,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F15,Q$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC16" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$11,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C16&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D16),COUNTIF($F$4:F15,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F15,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F15,R$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD16" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$12,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C16&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D16),COUNTIF($F$4:F15,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F15,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F15,S$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE16" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$13,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C16&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D16),COUNTIF($F$4:F15,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F15,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F15,T$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF16" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A16=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B16,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B16,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B16,1)&gt;='キャディ条件'!$Q$14,MOD($B16+$E16/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C16&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D16),COUNTIF($F$4:F15,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F15,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F15,U$3,$I$4:I15,"&gt;"&amp;$B16)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3079,7 +3974,7 @@
         <x:f>IF('ラウンド入力'!A17="","",IF('ラウンド入力'!E17="",'設定・説明'!$B$6,'ラウンド入力'!E17))</x:f>
       </x:c>
       <x:c r="F17" s="74" t="str">
-        <x:f>IF($A17="","",IF(COUNTIF(L17:U17,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L17:U17),L17:U17,0))))</x:f>
+        <x:f>IF($A17="","",IF(SUM(W17:AF17)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L17:U17),L17:U17,0))))</x:f>
       </x:c>
       <x:c r="G17" s="74" t="str">
         <x:f>IF(OR($F17="",$F17="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F17,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -3097,37 +3992,67 @@
         <x:f>IF($A17="","",IF($F17="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L17" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D17),COUNTIF($F$4:F16,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F16,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F16,L$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$5=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F16,L$3)=1,AND(COUNTIF($F$4:F16,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F16,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F16,L$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A17=""),"",IF(W17=1,100+IF('キャディ条件'!$H$5=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F16,L$3)=1,AND(COUNTIF($F$4:F16,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F16,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F16,L$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M17" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D17),COUNTIF($F$4:F16,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F16,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F16,M$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$6=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F16,M$3)=1,AND(COUNTIF($F$4:F16,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F16,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F16,M$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A17=""),"",IF(X17=1,100+IF('キャディ条件'!$H$6=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F16,M$3)=1,AND(COUNTIF($F$4:F16,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F16,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F16,M$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N17" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D17),COUNTIF($F$4:F16,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F16,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F16,N$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$7=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F16,N$3)=1,AND(COUNTIF($F$4:F16,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F16,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F16,N$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A17=""),"",IF(Y17=1,100+IF('キャディ条件'!$H$7=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F16,N$3)=1,AND(COUNTIF($F$4:F16,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F16,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F16,N$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O17" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D17),COUNTIF($F$4:F16,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F16,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F16,O$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$8=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F16,O$3)=1,AND(COUNTIF($F$4:F16,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F16,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F16,O$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A17=""),"",IF(Z17=1,100+IF('キャディ条件'!$H$8=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F16,O$3)=1,AND(COUNTIF($F$4:F16,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F16,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F16,O$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P17" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D17),COUNTIF($F$4:F16,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F16,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F16,P$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$9=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F16,P$3)=1,AND(COUNTIF($F$4:F16,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F16,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F16,P$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A17=""),"",IF(AA17=1,100+IF('キャディ条件'!$H$9=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F16,P$3)=1,AND(COUNTIF($F$4:F16,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F16,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F16,P$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q17" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D17),COUNTIF($F$4:F16,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F16,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F16,Q$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$10=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F16,Q$3)=1,AND(COUNTIF($F$4:F16,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F16,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F16,Q$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A17=""),"",IF(AB17=1,100+IF('キャディ条件'!$H$10=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F16,Q$3)=1,AND(COUNTIF($F$4:F16,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F16,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F16,Q$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R17" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D17),COUNTIF($F$4:F16,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F16,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F16,R$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$11=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F16,R$3)=1,AND(COUNTIF($F$4:F16,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F16,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F16,R$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A17=""),"",IF(AC17=1,100+IF('キャディ条件'!$H$11=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F16,R$3)=1,AND(COUNTIF($F$4:F16,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F16,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F16,R$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S17" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D17),COUNTIF($F$4:F16,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F16,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F16,S$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$12=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F16,S$3)=1,AND(COUNTIF($F$4:F16,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F16,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F16,S$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A17=""),"",IF(AD17=1,100+IF('キャディ条件'!$H$12=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F16,S$3)=1,AND(COUNTIF($F$4:F16,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F16,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F16,S$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T17" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D17),COUNTIF($F$4:F16,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F16,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F16,T$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$13=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F16,T$3)=1,AND(COUNTIF($F$4:F16,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F16,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F16,T$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A17=""),"",IF(AE17=1,100+IF('キャディ条件'!$H$13=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F16,T$3)=1,AND(COUNTIF($F$4:F16,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F16,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F16,T$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U17" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B17,2)&lt;=5)),$C17&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D17),COUNTIF($F$4:F16,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F16,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F16,U$3,$I$4:I16,"&gt;"&amp;$B17)=0),100+IF('キャディ条件'!$H$14=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F16,U$3)=1,AND(COUNTIF($F$4:F16,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F16,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F16,U$3,$C$4:C16,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A17=""),"",IF(AF17=1,100+IF('キャディ条件'!$H$14=$C17,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F16,U$3)=1,AND(COUNTIF($F$4:F16,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$18:$A$19,"&lt;&gt;",'ラウンド入力'!$B$18:$B$19,"&gt;="&amp;($B17+$E17/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$18:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$18:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C17=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F16,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F16,U$3,$C$4:C16,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V17" s="74" t="str">
         <x:f>IF($A17="","",IF($J17="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W17" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$5,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C17&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D17),COUNTIF($F$4:F16,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F16,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F16,L$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X17" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$6,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C17&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D17),COUNTIF($F$4:F16,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F16,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F16,M$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y17" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$7,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C17&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D17),COUNTIF($F$4:F16,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F16,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F16,N$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z17" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$8,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C17&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D17),COUNTIF($F$4:F16,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F16,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F16,O$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA17" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$9,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C17&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D17),COUNTIF($F$4:F16,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F16,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F16,P$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB17" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$10,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C17&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D17),COUNTIF($F$4:F16,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F16,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F16,Q$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC17" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$11,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C17&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D17),COUNTIF($F$4:F16,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F16,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F16,R$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD17" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$12,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C17&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D17),COUNTIF($F$4:F16,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F16,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F16,S$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE17" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$13,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C17&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D17),COUNTIF($F$4:F16,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F16,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F16,T$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF17" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A17=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B17,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B17,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B17,1)&gt;='キャディ条件'!$Q$14,MOD($B17+$E17/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C17&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D17),COUNTIF($F$4:F16,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F16,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F16,U$3,$I$4:I16,"&gt;"&amp;$B17)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3147,7 +4072,7 @@
         <x:f>IF('ラウンド入力'!A18="","",IF('ラウンド入力'!E18="",'設定・説明'!$B$6,'ラウンド入力'!E18))</x:f>
       </x:c>
       <x:c r="F18" s="74" t="str">
-        <x:f>IF($A18="","",IF(COUNTIF(L18:U18,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L18:U18),L18:U18,0))))</x:f>
+        <x:f>IF($A18="","",IF(SUM(W18:AF18)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L18:U18),L18:U18,0))))</x:f>
       </x:c>
       <x:c r="G18" s="74" t="str">
         <x:f>IF(OR($F18="",$F18="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F18,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -3165,37 +4090,67 @@
         <x:f>IF($A18="","",IF($F18="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L18" s="83" t="str">
-        <x:f>IF(OR(L$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D18),COUNTIF($F$4:F17,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F17,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F17,L$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$5=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F17,L$3)=1,AND(COUNTIF($F$4:F17,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$5))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F17,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F17,L$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A18=""),"",IF(W18=1,100+IF('キャディ条件'!$H$5=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F17,L$3)=1,AND(COUNTIF($F$4:F17,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F17,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F17,L$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M18" s="83" t="str">
-        <x:f>IF(OR(M$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D18),COUNTIF($F$4:F17,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F17,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F17,M$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$6=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F17,M$3)=1,AND(COUNTIF($F$4:F17,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$6))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F17,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F17,M$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A18=""),"",IF(X18=1,100+IF('キャディ条件'!$H$6=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F17,M$3)=1,AND(COUNTIF($F$4:F17,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F17,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F17,M$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N18" s="83" t="str">
-        <x:f>IF(OR(N$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D18),COUNTIF($F$4:F17,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F17,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F17,N$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$7=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F17,N$3)=1,AND(COUNTIF($F$4:F17,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$7))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F17,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F17,N$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A18=""),"",IF(Y18=1,100+IF('キャディ条件'!$H$7=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F17,N$3)=1,AND(COUNTIF($F$4:F17,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F17,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F17,N$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O18" s="83" t="str">
-        <x:f>IF(OR(O$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D18),COUNTIF($F$4:F17,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F17,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F17,O$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$8=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F17,O$3)=1,AND(COUNTIF($F$4:F17,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$8))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F17,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F17,O$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A18=""),"",IF(Z18=1,100+IF('キャディ条件'!$H$8=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F17,O$3)=1,AND(COUNTIF($F$4:F17,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F17,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F17,O$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P18" s="83" t="str">
-        <x:f>IF(OR(P$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D18),COUNTIF($F$4:F17,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F17,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F17,P$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$9=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F17,P$3)=1,AND(COUNTIF($F$4:F17,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$9))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F17,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F17,P$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A18=""),"",IF(AA18=1,100+IF('キャディ条件'!$H$9=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F17,P$3)=1,AND(COUNTIF($F$4:F17,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F17,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F17,P$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q18" s="83" t="str">
-        <x:f>IF(OR(Q$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D18),COUNTIF($F$4:F17,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F17,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F17,Q$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$10=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F17,Q$3)=1,AND(COUNTIF($F$4:F17,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$10))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F17,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F17,Q$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A18=""),"",IF(AB18=1,100+IF('キャディ条件'!$H$10=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F17,Q$3)=1,AND(COUNTIF($F$4:F17,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F17,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F17,Q$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R18" s="83" t="str">
-        <x:f>IF(OR(R$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D18),COUNTIF($F$4:F17,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F17,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F17,R$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$11=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F17,R$3)=1,AND(COUNTIF($F$4:F17,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$11))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F17,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F17,R$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A18=""),"",IF(AC18=1,100+IF('キャディ条件'!$H$11=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F17,R$3)=1,AND(COUNTIF($F$4:F17,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F17,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F17,R$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S18" s="83" t="str">
-        <x:f>IF(OR(S$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D18),COUNTIF($F$4:F17,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F17,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F17,S$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$12=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F17,S$3)=1,AND(COUNTIF($F$4:F17,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$12))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F17,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F17,S$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A18=""),"",IF(AD18=1,100+IF('キャディ条件'!$H$12=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F17,S$3)=1,AND(COUNTIF($F$4:F17,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F17,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F17,S$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T18" s="83" t="str">
-        <x:f>IF(OR(T$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D18),COUNTIF($F$4:F17,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F17,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F17,T$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$13=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F17,T$3)=1,AND(COUNTIF($F$4:F17,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$13))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F17,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F17,T$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A18=""),"",IF(AE18=1,100+IF('キャディ条件'!$H$13=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F17,T$3)=1,AND(COUNTIF($F$4:F17,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F17,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F17,T$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U18" s="83" t="str">
-        <x:f>IF(OR(U$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B18,2)&lt;=5)),$C18&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D18),COUNTIF($F$4:F17,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F17,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F17,U$3,$I$4:I17,"&gt;"&amp;$B18)=0),100+IF('キャディ条件'!$H$14=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F17,U$3)=1,AND(COUNTIF($F$4:F17,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$14))&gt;0))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F17,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F17,U$3,$C$4:C17,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A18=""),"",IF(AF18=1,100+IF('キャディ条件'!$H$14=$C18,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F17,U$3)=1,AND(COUNTIF($F$4:F17,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$19:$A$19,"&lt;&gt;",'ラウンド入力'!$B$19:$B$19,"&gt;="&amp;($B18+$E18/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$19:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$19:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C18=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F17,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F17,U$3,$C$4:C17,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V18" s="74" t="str">
         <x:f>IF($A18="","",IF($J18="人数希望一致",1,0))</x:f>
+      </x:c>
+      <x:c r="W18" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$5,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C18&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D18),COUNTIF($F$4:F17,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F17,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F17,L$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X18" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$6,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C18&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D18),COUNTIF($F$4:F17,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F17,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F17,M$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y18" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$7,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C18&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D18),COUNTIF($F$4:F17,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F17,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F17,N$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z18" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$8,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C18&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D18),COUNTIF($F$4:F17,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F17,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F17,O$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA18" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$9,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C18&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D18),COUNTIF($F$4:F17,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F17,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F17,P$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB18" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$10,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C18&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D18),COUNTIF($F$4:F17,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F17,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F17,Q$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC18" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$11,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C18&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D18),COUNTIF($F$4:F17,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F17,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F17,R$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD18" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$12,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C18&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D18),COUNTIF($F$4:F17,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F17,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F17,S$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE18" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$13,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C18&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D18),COUNTIF($F$4:F17,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F17,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F17,T$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF18" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A18=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B18,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B18,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B18,1)&gt;='キャディ条件'!$Q$14,MOD($B18+$E18/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C18&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D18),COUNTIF($F$4:F17,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F17,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F17,U$3,$I$4:I17,"&gt;"&amp;$B18)=0),1,0))</x:f>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -3215,7 +4170,7 @@
         <x:f>IF('ラウンド入力'!A19="","",IF('ラウンド入力'!E19="",'設定・説明'!$B$6,'ラウンド入力'!E19))</x:f>
       </x:c>
       <x:c r="F19" s="77" t="str">
-        <x:f>IF($A19="","",IF(COUNTIF(L19:U19,"&gt;-9999")=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L19:U19),L19:U19,0))))</x:f>
+        <x:f>IF($A19="","",IF(SUM(W19:AF19)=0,"未割当",INDEX($L$3:$U$3,1,MATCH(MAX(L19:U19),L19:U19,0))))</x:f>
       </x:c>
       <x:c r="G19" s="77" t="str">
         <x:f>IF(OR($F19="",$F19="未割当"),"",INDEX('キャディ条件'!$B$5:$B$14,MATCH($F19,'キャディ条件'!$A$5:$A$14,0)))</x:f>
@@ -3233,43 +4188,73 @@
         <x:f>IF($A19="","",IF($F19="未割当","要手動調整",""))</x:f>
       </x:c>
       <x:c r="L19" s="84" t="str">
-        <x:f>IF(OR(L$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D19),COUNTIF($F$4:F18,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F18,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F18,L$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$5=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F18,L$3)=1,AND(COUNTIF($F$4:F18,L$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F18,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F18,L$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(L$3="",$A19=""),"",IF(W19=1,100+IF('キャディ条件'!$H$5=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$5="はい",'キャディ条件'!$F$5="はい",OR(COUNTIF($F$4:F18,L$3)=1,AND(COUNTIF($F$4:F18,L$3)=0,IF('キャディ条件'!$J$5="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$5),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$5,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$5))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$5="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$5+COUNTIF($F$4:F18,L$3))*'設定・説明'!$B$11-('キャディ条件'!$L$5+COUNTIFS($F$4:F18,L$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="M19" s="84" t="str">
-        <x:f>IF(OR(M$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D19),COUNTIF($F$4:F18,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F18,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F18,M$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$6=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F18,M$3)=1,AND(COUNTIF($F$4:F18,M$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F18,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F18,M$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(M$3="",$A19=""),"",IF(X19=1,100+IF('キャディ条件'!$H$6=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$6="はい",'キャディ条件'!$F$6="はい",OR(COUNTIF($F$4:F18,M$3)=1,AND(COUNTIF($F$4:F18,M$3)=0,IF('キャディ条件'!$J$6="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$6),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$6,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$6))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$6="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$6+COUNTIF($F$4:F18,M$3))*'設定・説明'!$B$11-('キャディ条件'!$L$6+COUNTIFS($F$4:F18,M$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="N19" s="84" t="str">
-        <x:f>IF(OR(N$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D19),COUNTIF($F$4:F18,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F18,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F18,N$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$7=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F18,N$3)=1,AND(COUNTIF($F$4:F18,N$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F18,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F18,N$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(N$3="",$A19=""),"",IF(Y19=1,100+IF('キャディ条件'!$H$7=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$7="はい",'キャディ条件'!$F$7="はい",OR(COUNTIF($F$4:F18,N$3)=1,AND(COUNTIF($F$4:F18,N$3)=0,IF('キャディ条件'!$J$7="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$7),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$7,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$7))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$7="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$7+COUNTIF($F$4:F18,N$3))*'設定・説明'!$B$11-('キャディ条件'!$L$7+COUNTIFS($F$4:F18,N$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="O19" s="84" t="str">
-        <x:f>IF(OR(O$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D19),COUNTIF($F$4:F18,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F18,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F18,O$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$8=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F18,O$3)=1,AND(COUNTIF($F$4:F18,O$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F18,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F18,O$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(O$3="",$A19=""),"",IF(Z19=1,100+IF('キャディ条件'!$H$8=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$8="はい",'キャディ条件'!$F$8="はい",OR(COUNTIF($F$4:F18,O$3)=1,AND(COUNTIF($F$4:F18,O$3)=0,IF('キャディ条件'!$J$8="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$8),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$8,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$8))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$8="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$8+COUNTIF($F$4:F18,O$3))*'設定・説明'!$B$11-('キャディ条件'!$L$8+COUNTIFS($F$4:F18,O$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="P19" s="84" t="str">
-        <x:f>IF(OR(P$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D19),COUNTIF($F$4:F18,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F18,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F18,P$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$9=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F18,P$3)=1,AND(COUNTIF($F$4:F18,P$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F18,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F18,P$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(P$3="",$A19=""),"",IF(AA19=1,100+IF('キャディ条件'!$H$9=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$9="はい",'キャディ条件'!$F$9="はい",OR(COUNTIF($F$4:F18,P$3)=1,AND(COUNTIF($F$4:F18,P$3)=0,IF('キャディ条件'!$J$9="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$9),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$9,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$9))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$9="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$9+COUNTIF($F$4:F18,P$3))*'設定・説明'!$B$11-('キャディ条件'!$L$9+COUNTIFS($F$4:F18,P$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="Q19" s="84" t="str">
-        <x:f>IF(OR(Q$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D19),COUNTIF($F$4:F18,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F18,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F18,Q$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$10=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F18,Q$3)=1,AND(COUNTIF($F$4:F18,Q$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F18,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F18,Q$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(Q$3="",$A19=""),"",IF(AB19=1,100+IF('キャディ条件'!$H$10=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$10="はい",'キャディ条件'!$F$10="はい",OR(COUNTIF($F$4:F18,Q$3)=1,AND(COUNTIF($F$4:F18,Q$3)=0,IF('キャディ条件'!$J$10="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$10),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$10,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$10))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$10="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$10+COUNTIF($F$4:F18,Q$3))*'設定・説明'!$B$11-('キャディ条件'!$L$10+COUNTIFS($F$4:F18,Q$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="R19" s="84" t="str">
-        <x:f>IF(OR(R$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D19),COUNTIF($F$4:F18,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F18,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F18,R$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$11=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F18,R$3)=1,AND(COUNTIF($F$4:F18,R$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F18,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F18,R$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(R$3="",$A19=""),"",IF(AC19=1,100+IF('キャディ条件'!$H$11=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$11="はい",'キャディ条件'!$F$11="はい",OR(COUNTIF($F$4:F18,R$3)=1,AND(COUNTIF($F$4:F18,R$3)=0,IF('キャディ条件'!$J$11="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$11),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$11,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$11))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$11="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$11+COUNTIF($F$4:F18,R$3))*'設定・説明'!$B$11-('キャディ条件'!$L$11+COUNTIFS($F$4:F18,R$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="S19" s="84" t="str">
-        <x:f>IF(OR(S$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D19),COUNTIF($F$4:F18,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F18,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F18,S$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$12=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F18,S$3)=1,AND(COUNTIF($F$4:F18,S$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F18,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F18,S$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(S$3="",$A19=""),"",IF(AD19=1,100+IF('キャディ条件'!$H$12=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$12="はい",'キャディ条件'!$F$12="はい",OR(COUNTIF($F$4:F18,S$3)=1,AND(COUNTIF($F$4:F18,S$3)=0,IF('キャディ条件'!$J$12="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$12),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$12,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$12))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$12="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$12+COUNTIF($F$4:F18,S$3))*'設定・説明'!$B$11-('キャディ条件'!$L$12+COUNTIFS($F$4:F18,S$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="T19" s="84" t="str">
-        <x:f>IF(OR(T$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D19),COUNTIF($F$4:F18,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F18,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F18,T$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$13=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F18,T$3)=1,AND(COUNTIF($F$4:F18,T$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F18,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F18,T$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(T$3="",$A19=""),"",IF(AE19=1,100+IF('キャディ条件'!$H$13=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$13="はい",'キャディ条件'!$F$13="はい",OR(COUNTIF($F$4:F18,T$3)=1,AND(COUNTIF($F$4:F18,T$3)=0,IF('キャディ条件'!$J$13="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$13),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$13,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$13))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$13="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$13+COUNTIF($F$4:F18,T$3))*'設定・説明'!$B$11-('キャディ条件'!$L$13+COUNTIFS($F$4:F18,T$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="U19" s="84" t="str">
-        <x:f>IF(OR(U$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B19,2)&lt;=5)),$C19&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D19),COUNTIF($F$4:F18,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F18,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F18,U$3,$I$4:I18,"&gt;"&amp;$B19)=0),100+IF('キャディ条件'!$H$14=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F18,U$3)=1,AND(COUNTIF($F$4:F18,U$3)=0,FALSE))),'設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F18,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F18,U$3,$C$4:C18,4))*'設定・説明'!$B$12,-9999))</x:f>
+        <x:f>IF(OR(U$3="",$A19=""),"",IF(AF19=1,100+IF('キャディ条件'!$H$14=$C19,'設定・説明'!$B$9,0)+IF(AND('キャディ条件'!$E$14="はい",'キャディ条件'!$F$14="はい",OR(COUNTIF($F$4:F18,U$3)=1,AND(COUNTIF($F$4:F18,U$3)=0,IF('キャディ条件'!$J$14="全コース",COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$14),COUNTIFS('ラウンド入力'!$A$20:$A$19,"&lt;&gt;",'ラウンド入力'!$B$20:$B$19,"&gt;="&amp;($B19+$E19/1440+'設定・説明'!$B$7/1440),'ラウンド入力'!$C$20:$C$19,"&lt;="&amp;'キャディ条件'!$G$14,'ラウンド入力'!$D$20:$D$19,'キャディ条件'!$J$14))&gt;0))), '設定・説明'!$B$10,0)+IF(AND('キャディ条件'!$I$14="ベテラン",$C19=4),'設定・説明'!$B$13,0)-('キャディ条件'!$K$14+COUNTIF($F$4:F18,U$3))*'設定・説明'!$B$11-('キャディ条件'!$L$14+COUNTIFS($F$4:F18,U$3,$C$4:C18,4))*'設定・説明'!$B$12,""))</x:f>
       </x:c>
       <x:c r="V19" s="77" t="str">
         <x:f>IF($A19="","",IF($J19="人数希望一致",1,0))</x:f>
       </x:c>
+      <x:c r="W19" s="202" t="str">
+        <x:f>IF(OR(L$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,L$3)=1,OR('キャディ条件'!$C$5="全日",AND('キャディ条件'!$C$5="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$5="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$5="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$5,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$5,$C19&lt;='キャディ条件'!$G$5,OR('キャディ条件'!$J$5="全コース",'キャディ条件'!$J$5=$D19),COUNTIF($F$4:F18,L$3)&lt;'キャディ条件'!$D$5,OR(COUNTIF($F$4:F18,L$3)=0,'キャディ条件'!$E$5="はい"),COUNTIFS($F$4:F18,L$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="X19" s="203" t="str">
+        <x:f>IF(OR(M$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,M$3)=1,OR('キャディ条件'!$C$6="全日",AND('キャディ条件'!$C$6="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$6="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$6="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$6,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$6,$C19&lt;='キャディ条件'!$G$6,OR('キャディ条件'!$J$6="全コース",'キャディ条件'!$J$6=$D19),COUNTIF($F$4:F18,M$3)&lt;'キャディ条件'!$D$6,OR(COUNTIF($F$4:F18,M$3)=0,'キャディ条件'!$E$6="はい"),COUNTIFS($F$4:F18,M$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Y19" s="203" t="str">
+        <x:f>IF(OR(N$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,N$3)=1,OR('キャディ条件'!$C$7="全日",AND('キャディ条件'!$C$7="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$7="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$7="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$7,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$7,$C19&lt;='キャディ条件'!$G$7,OR('キャディ条件'!$J$7="全コース",'キャディ条件'!$J$7=$D19),COUNTIF($F$4:F18,N$3)&lt;'キャディ条件'!$D$7,OR(COUNTIF($F$4:F18,N$3)=0,'キャディ条件'!$E$7="はい"),COUNTIFS($F$4:F18,N$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="Z19" s="203" t="str">
+        <x:f>IF(OR(O$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,O$3)=1,OR('キャディ条件'!$C$8="全日",AND('キャディ条件'!$C$8="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$8="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$8="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$8,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$8,$C19&lt;='キャディ条件'!$G$8,OR('キャディ条件'!$J$8="全コース",'キャディ条件'!$J$8=$D19),COUNTIF($F$4:F18,O$3)&lt;'キャディ条件'!$D$8,OR(COUNTIF($F$4:F18,O$3)=0,'キャディ条件'!$E$8="はい"),COUNTIFS($F$4:F18,O$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AA19" s="203" t="str">
+        <x:f>IF(OR(P$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,P$3)=1,OR('キャディ条件'!$C$9="全日",AND('キャディ条件'!$C$9="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$9="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$9="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$9,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$9,$C19&lt;='キャディ条件'!$G$9,OR('キャディ条件'!$J$9="全コース",'キャディ条件'!$J$9=$D19),COUNTIF($F$4:F18,P$3)&lt;'キャディ条件'!$D$9,OR(COUNTIF($F$4:F18,P$3)=0,'キャディ条件'!$E$9="はい"),COUNTIFS($F$4:F18,P$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AB19" s="203" t="str">
+        <x:f>IF(OR(Q$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,Q$3)=1,OR('キャディ条件'!$C$10="全日",AND('キャディ条件'!$C$10="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$10="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$10="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$10,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$10,$C19&lt;='キャディ条件'!$G$10,OR('キャディ条件'!$J$10="全コース",'キャディ条件'!$J$10=$D19),COUNTIF($F$4:F18,Q$3)&lt;'キャディ条件'!$D$10,OR(COUNTIF($F$4:F18,Q$3)=0,'キャディ条件'!$E$10="はい"),COUNTIFS($F$4:F18,Q$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AC19" s="203" t="str">
+        <x:f>IF(OR(R$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,R$3)=1,OR('キャディ条件'!$C$11="全日",AND('キャディ条件'!$C$11="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$11="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$11="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$11,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$11,$C19&lt;='キャディ条件'!$G$11,OR('キャディ条件'!$J$11="全コース",'キャディ条件'!$J$11=$D19),COUNTIF($F$4:F18,R$3)&lt;'キャディ条件'!$D$11,OR(COUNTIF($F$4:F18,R$3)=0,'キャディ条件'!$E$11="はい"),COUNTIFS($F$4:F18,R$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AD19" s="203" t="str">
+        <x:f>IF(OR(S$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,S$3)=1,OR('キャディ条件'!$C$12="全日",AND('キャディ条件'!$C$12="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$12="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$12="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$12,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$12,$C19&lt;='キャディ条件'!$G$12,OR('キャディ条件'!$J$12="全コース",'キャディ条件'!$J$12=$D19),COUNTIF($F$4:F18,S$3)&lt;'キャディ条件'!$D$12,OR(COUNTIF($F$4:F18,S$3)=0,'キャディ条件'!$E$12="はい"),COUNTIFS($F$4:F18,S$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AE19" s="203" t="str">
+        <x:f>IF(OR(T$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,T$3)=1,OR('キャディ条件'!$C$13="全日",AND('キャディ条件'!$C$13="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$13="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$13="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$13,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$13,$C19&lt;='キャディ条件'!$G$13,OR('キャディ条件'!$J$13="全コース",'キャディ条件'!$J$13=$D19),COUNTIF($F$4:F18,T$3)&lt;'キャディ条件'!$D$13,OR(COUNTIF($F$4:F18,T$3)=0,'キャディ条件'!$E$13="はい"),COUNTIFS($F$4:F18,T$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
+      <x:c r="AF19" s="203" t="str">
+        <x:f>IF(OR(U$3="",$A19=""),"",IF(AND(COUNTIF('キャディ条件'!$A$5:$A$14,U$3)=1,OR('キャディ条件'!$C$14="全日",AND('キャディ条件'!$C$14="土日",WEEKDAY($B19,2)&gt;=6),AND('キャディ条件'!$C$14="平日",WEEKDAY($B19,2)&lt;=5)),'キャディ条件'!$P$14="はい",MOD($B19,1)&gt;='キャディ条件'!$Q$14,MOD($B19+$E19/1440+'設定・説明'!$B$7/1440,1)&lt;='キャディ条件'!$R$14,$C19&lt;='キャディ条件'!$G$14,OR('キャディ条件'!$J$14="全コース",'キャディ条件'!$J$14=$D19),COUNTIF($F$4:F18,U$3)&lt;'キャディ条件'!$D$14,OR(COUNTIF($F$4:F18,U$3)=0,'キャディ条件'!$E$14="はい"),COUNTIFS($F$4:F18,U$3,$I$4:I18,"&gt;"&amp;$B19)=0),1,0))</x:f>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:V1"/>
-    <x:mergeCell ref="A2:V2"/>
+    <x:mergeCell ref="A1:AF1"/>
+    <x:mergeCell ref="A2:AF2"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="F5:F19">
     <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="未割当"/>
@@ -3282,8 +4267,19 @@
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="W5:AF19">
+    <x:cfRule type="cellIs" dxfId="10" priority="4">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="11" priority="5">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="12" priority="6">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R063d9e65e2454623"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62947e7a69494035"/>
 </x:worksheet>
 </file>
 
@@ -4323,7 +5319,7 @@
         <x:v>一時制限あり（期限表示）</x:v>
       </x:c>
       <x:c r="H24" s="105" t="str">
-        <x:v>CourseBoardローカル。詳細理由は限定管理</x:v>
+        <x:v>CourseBoardローカル。最大人数・対象コース・有効期限のみ保存（病名・介護・詳細理由は保存しない）</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
